--- a/research/traditional_assets/database/data/lithuania/lithuania_retail_special_lines.xlsx
+++ b/research/traditional_assets/database/data/lithuania/lithuania_retail_special_lines.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09915159956694841</v>
+        <v>0.09904112216759797</v>
       </c>
       <c r="C2">
-        <v>238.0031416413956</v>
+        <v>236.1308843653892</v>
       </c>
       <c r="D2">
-        <v>230.2331416413956</v>
+        <v>230.7108843653892</v>
       </c>
       <c r="E2">
-        <v>-67.59999999999999</v>
+        <v>-65.25</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="G2">
         <v>7.77</v>
@@ -1451,28 +1451,28 @@
         <v>23.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.118205</v>
       </c>
       <c r="N2">
-        <v>23.5</v>
+        <v>23.381795</v>
       </c>
       <c r="O2">
-        <v>3.525</v>
+        <v>3.50726925</v>
       </c>
       <c r="P2">
-        <v>19.975</v>
+        <v>19.87452575</v>
       </c>
       <c r="Q2">
-        <v>27.175</v>
+        <v>27.07452575</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09915159956694841</v>
+        <v>0.09960966885615957</v>
       </c>
       <c r="T2">
-        <v>0.9771532823765237</v>
+        <v>0.9855429822757159</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>198.8071570576541</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09904112216759797</v>
+        <v>0.09893064476824756</v>
       </c>
       <c r="C3">
-        <v>236.1308843653892</v>
+        <v>234.2606138815225</v>
       </c>
       <c r="D3">
-        <v>230.7108843653892</v>
+        <v>231.1906138815225</v>
       </c>
       <c r="E3">
-        <v>-65.25</v>
+        <v>-62.89999999999999</v>
       </c>
       <c r="F3">
-        <v>2.35</v>
+        <v>4.7</v>
       </c>
       <c r="G3">
         <v>7.77</v>
@@ -1533,28 +1533,28 @@
         <v>23.5</v>
       </c>
       <c r="M3">
-        <v>0.118205</v>
+        <v>0.23641</v>
       </c>
       <c r="N3">
-        <v>23.381795</v>
+        <v>23.26359</v>
       </c>
       <c r="O3">
-        <v>3.50726925</v>
+        <v>3.4895385</v>
       </c>
       <c r="P3">
-        <v>19.87452575</v>
+        <v>19.7740515</v>
       </c>
       <c r="Q3">
-        <v>27.07452575</v>
+        <v>26.9740515</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09960966885615957</v>
+        <v>0.1000770864982118</v>
       </c>
       <c r="T3">
-        <v>0.9855429822757159</v>
+        <v>0.9941039005401981</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>198.8071570576541</v>
+        <v>99.40357852882704</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09893064476824756</v>
+        <v>0.09882016736889712</v>
       </c>
       <c r="C4">
-        <v>234.2606138815225</v>
+        <v>232.3923426093508</v>
       </c>
       <c r="D4">
-        <v>231.1906138815225</v>
+        <v>231.6723426093508</v>
       </c>
       <c r="E4">
-        <v>-62.89999999999999</v>
+        <v>-60.55</v>
       </c>
       <c r="F4">
-        <v>4.7</v>
+        <v>7.05</v>
       </c>
       <c r="G4">
         <v>7.77</v>
@@ -1615,28 +1615,28 @@
         <v>23.5</v>
       </c>
       <c r="M4">
-        <v>0.23641</v>
+        <v>0.354615</v>
       </c>
       <c r="N4">
-        <v>23.26359</v>
+        <v>23.145385</v>
       </c>
       <c r="O4">
-        <v>3.4895385</v>
+        <v>3.47180775</v>
       </c>
       <c r="P4">
-        <v>19.7740515</v>
+        <v>19.67357725</v>
       </c>
       <c r="Q4">
-        <v>26.9740515</v>
+        <v>26.87357725</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1000770864982118</v>
+        <v>0.1005541416174197</v>
       </c>
       <c r="T4">
-        <v>0.9941039005401981</v>
+        <v>1.002841332583329</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>99.40357852882704</v>
+        <v>66.26905235255137</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09882016736889712</v>
+        <v>0.09870968996954671</v>
       </c>
       <c r="C5">
-        <v>232.3923426093508</v>
+        <v>230.5260830721588</v>
       </c>
       <c r="D5">
-        <v>231.6723426093508</v>
+        <v>232.1560830721588</v>
       </c>
       <c r="E5">
-        <v>-60.55</v>
+        <v>-58.2</v>
       </c>
       <c r="F5">
-        <v>7.05</v>
+        <v>9.4</v>
       </c>
       <c r="G5">
         <v>7.77</v>
@@ -1697,28 +1697,28 @@
         <v>23.5</v>
       </c>
       <c r="M5">
-        <v>0.354615</v>
+        <v>0.47282</v>
       </c>
       <c r="N5">
-        <v>23.145385</v>
+        <v>23.02718</v>
       </c>
       <c r="O5">
-        <v>3.47180775</v>
+        <v>3.454077</v>
       </c>
       <c r="P5">
-        <v>19.67357725</v>
+        <v>19.573103</v>
       </c>
       <c r="Q5">
-        <v>26.87357725</v>
+        <v>26.773103</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1005541416174197</v>
+        <v>0.1010411353849445</v>
       </c>
       <c r="T5">
-        <v>1.002841332583329</v>
+        <v>1.011760794460692</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>66.26905235255137</v>
+        <v>49.70178926441352</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09870968996954671</v>
+        <v>0.09859921257019627</v>
       </c>
       <c r="C6">
-        <v>230.5260830721588</v>
+        <v>228.6618478980471</v>
       </c>
       <c r="D6">
-        <v>232.1560830721588</v>
+        <v>232.641847898047</v>
       </c>
       <c r="E6">
-        <v>-58.2</v>
+        <v>-55.84999999999999</v>
       </c>
       <c r="F6">
-        <v>9.4</v>
+        <v>11.75</v>
       </c>
       <c r="G6">
         <v>7.77</v>
@@ -1779,28 +1779,28 @@
         <v>23.5</v>
       </c>
       <c r="M6">
-        <v>0.47282</v>
+        <v>0.591025</v>
       </c>
       <c r="N6">
-        <v>23.02718</v>
+        <v>22.908975</v>
       </c>
       <c r="O6">
-        <v>3.454077</v>
+        <v>3.43634625</v>
       </c>
       <c r="P6">
-        <v>19.573103</v>
+        <v>19.47262875</v>
       </c>
       <c r="Q6">
-        <v>26.773103</v>
+        <v>26.67262875</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1010411353849445</v>
+        <v>0.1015383816528382</v>
       </c>
       <c r="T6">
-        <v>1.011760794460692</v>
+        <v>1.020868034482842</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>49.70178926441352</v>
+        <v>39.76143141153081</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09859921257019627</v>
+        <v>0.09848873517084586</v>
       </c>
       <c r="C7">
-        <v>228.6618478980471</v>
+        <v>226.7996498210295</v>
       </c>
       <c r="D7">
-        <v>232.641847898047</v>
+        <v>233.1296498210295</v>
       </c>
       <c r="E7">
-        <v>-55.84999999999999</v>
+        <v>-53.49999999999999</v>
       </c>
       <c r="F7">
-        <v>11.75</v>
+        <v>14.1</v>
       </c>
       <c r="G7">
         <v>7.77</v>
@@ -1861,28 +1861,28 @@
         <v>23.5</v>
       </c>
       <c r="M7">
-        <v>0.591025</v>
+        <v>0.70923</v>
       </c>
       <c r="N7">
-        <v>22.908975</v>
+        <v>22.79077</v>
       </c>
       <c r="O7">
-        <v>3.43634625</v>
+        <v>3.4186155</v>
       </c>
       <c r="P7">
-        <v>19.47262875</v>
+        <v>19.3721545</v>
       </c>
       <c r="Q7">
-        <v>26.67262875</v>
+        <v>26.5721545</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1015383816528382</v>
+        <v>0.1020462076285594</v>
       </c>
       <c r="T7">
-        <v>1.020868034482842</v>
+        <v>1.030169045569292</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>39.76143141153081</v>
+        <v>33.13452617627568</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09848873517084586</v>
+        <v>0.09837825777149545</v>
       </c>
       <c r="C8">
-        <v>226.7996498210295</v>
+        <v>224.9395016821473</v>
       </c>
       <c r="D8">
-        <v>233.1296498210295</v>
+        <v>233.6195016821473</v>
       </c>
       <c r="E8">
-        <v>-53.49999999999999</v>
+        <v>-51.14999999999999</v>
       </c>
       <c r="F8">
-        <v>14.1</v>
+        <v>16.45</v>
       </c>
       <c r="G8">
         <v>7.77</v>
@@ -1943,28 +1943,28 @@
         <v>23.5</v>
       </c>
       <c r="M8">
-        <v>0.7092299999999999</v>
+        <v>0.8274349999999999</v>
       </c>
       <c r="N8">
-        <v>22.79077</v>
+        <v>22.672565</v>
       </c>
       <c r="O8">
-        <v>3.4186155</v>
+        <v>3.40088475</v>
       </c>
       <c r="P8">
-        <v>19.3721545</v>
+        <v>19.27168025</v>
       </c>
       <c r="Q8">
-        <v>26.5721545</v>
+        <v>26.47168025</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1020462076285594</v>
+        <v>0.1025649545930059</v>
       </c>
       <c r="T8">
-        <v>1.030169045569292</v>
+        <v>1.039670078399538</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>33.13452617627568</v>
+        <v>28.40102243680773</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09837825777149545</v>
+        <v>0.09826778037214502</v>
       </c>
       <c r="C9">
-        <v>224.9395016821473</v>
+        <v>223.0814164305952</v>
       </c>
       <c r="D9">
-        <v>233.6195016821473</v>
+        <v>234.1114164305952</v>
       </c>
       <c r="E9">
-        <v>-51.14999999999999</v>
+        <v>-48.8</v>
       </c>
       <c r="F9">
-        <v>16.45</v>
+        <v>18.8</v>
       </c>
       <c r="G9">
         <v>7.77</v>
@@ -2025,28 +2025,28 @@
         <v>23.5</v>
       </c>
       <c r="M9">
-        <v>0.8274350000000001</v>
+        <v>0.94564</v>
       </c>
       <c r="N9">
-        <v>22.672565</v>
+        <v>22.55436</v>
       </c>
       <c r="O9">
-        <v>3.40088475</v>
+        <v>3.383154</v>
       </c>
       <c r="P9">
-        <v>19.27168025</v>
+        <v>19.171206</v>
       </c>
       <c r="Q9">
-        <v>26.47168025</v>
+        <v>26.371206</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1025649545930059</v>
+        <v>0.103094978665375</v>
       </c>
       <c r="T9">
-        <v>1.039670078399538</v>
+        <v>1.049377655421745</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.40102243680772</v>
+        <v>24.85089463220676</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09826778037214502</v>
+        <v>0.0981573029727946</v>
       </c>
       <c r="C10">
-        <v>223.0814164305952</v>
+        <v>221.2254071248626</v>
       </c>
       <c r="D10">
-        <v>234.1114164305952</v>
+        <v>234.6054071248626</v>
       </c>
       <c r="E10">
-        <v>-48.8</v>
+        <v>-46.45</v>
       </c>
       <c r="F10">
-        <v>18.8</v>
+        <v>21.15</v>
       </c>
       <c r="G10">
         <v>7.77</v>
@@ -2107,28 +2107,28 @@
         <v>23.5</v>
       </c>
       <c r="M10">
-        <v>0.94564</v>
+        <v>1.063845</v>
       </c>
       <c r="N10">
-        <v>22.55436</v>
+        <v>22.436155</v>
       </c>
       <c r="O10">
-        <v>3.383154</v>
+        <v>3.36542325</v>
       </c>
       <c r="P10">
-        <v>19.171206</v>
+        <v>19.07073175</v>
       </c>
       <c r="Q10">
-        <v>26.371206</v>
+        <v>26.27073175</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.103094978665375</v>
+        <v>0.1036366516184556</v>
       </c>
       <c r="T10">
-        <v>1.049377655421745</v>
+        <v>1.059298585785099</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.85089463220676</v>
+        <v>22.08968411751712</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0981573029727946</v>
+        <v>0.09804682557344419</v>
       </c>
       <c r="C11">
-        <v>221.2254071248626</v>
+        <v>219.3714869338888</v>
       </c>
       <c r="D11">
-        <v>234.6054071248626</v>
+        <v>235.1014869338888</v>
       </c>
       <c r="E11">
-        <v>-46.45</v>
+        <v>-44.09999999999999</v>
       </c>
       <c r="F11">
-        <v>21.15</v>
+        <v>23.5</v>
       </c>
       <c r="G11">
         <v>7.77</v>
@@ -2189,28 +2189,28 @@
         <v>23.5</v>
       </c>
       <c r="M11">
-        <v>1.063845</v>
+        <v>1.18205</v>
       </c>
       <c r="N11">
-        <v>22.436155</v>
+        <v>22.31795</v>
       </c>
       <c r="O11">
-        <v>3.36542325</v>
+        <v>3.3476925</v>
       </c>
       <c r="P11">
-        <v>19.07073175</v>
+        <v>18.9702575</v>
       </c>
       <c r="Q11">
-        <v>26.27073175</v>
+        <v>26.1702575</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1036366516184556</v>
+        <v>0.1041903617482713</v>
       </c>
       <c r="T11">
-        <v>1.059298585785099</v>
+        <v>1.06943998126764</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.08968411751712</v>
+        <v>19.88071570576541</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09804682557344419</v>
+        <v>0.09793634817409376</v>
       </c>
       <c r="C12">
-        <v>219.3714869338888</v>
+        <v>217.5196691382339</v>
       </c>
       <c r="D12">
-        <v>235.1014869338888</v>
+        <v>235.5996691382339</v>
       </c>
       <c r="E12">
-        <v>-44.09999999999999</v>
+        <v>-41.74999999999999</v>
       </c>
       <c r="F12">
-        <v>23.5</v>
+        <v>25.85</v>
       </c>
       <c r="G12">
         <v>7.77</v>
@@ -2271,28 +2271,28 @@
         <v>23.5</v>
       </c>
       <c r="M12">
-        <v>1.18205</v>
+        <v>1.300255</v>
       </c>
       <c r="N12">
-        <v>22.31795</v>
+        <v>22.199745</v>
       </c>
       <c r="O12">
-        <v>3.3476925</v>
+        <v>3.32996175</v>
       </c>
       <c r="P12">
-        <v>18.9702575</v>
+        <v>18.86978325</v>
       </c>
       <c r="Q12">
-        <v>26.1702575</v>
+        <v>26.06978325</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1041903617482713</v>
+        <v>0.1047565148023525</v>
       </c>
       <c r="T12">
-        <v>1.06943998126764</v>
+        <v>1.079809273277878</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.88071570576541</v>
+        <v>18.07337791433219</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09793634817409376</v>
+        <v>0.09782587077474333</v>
       </c>
       <c r="C13">
-        <v>217.5196691382339</v>
+        <v>215.6699671312634</v>
       </c>
       <c r="D13">
-        <v>235.5996691382339</v>
+        <v>236.0999671312634</v>
       </c>
       <c r="E13">
-        <v>-41.74999999999999</v>
+        <v>-39.39999999999999</v>
       </c>
       <c r="F13">
-        <v>25.85</v>
+        <v>28.2</v>
       </c>
       <c r="G13">
         <v>7.77</v>
@@ -2353,28 +2353,28 @@
         <v>23.5</v>
       </c>
       <c r="M13">
-        <v>1.300255</v>
+        <v>1.41846</v>
       </c>
       <c r="N13">
-        <v>22.199745</v>
+        <v>22.08154</v>
       </c>
       <c r="O13">
-        <v>3.32996175</v>
+        <v>3.312231</v>
       </c>
       <c r="P13">
-        <v>18.86978325</v>
+        <v>18.769309</v>
       </c>
       <c r="Q13">
-        <v>26.06978325</v>
+        <v>25.969309</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1047565148023525</v>
+        <v>0.1053355349712992</v>
       </c>
       <c r="T13">
-        <v>1.079809273277878</v>
+        <v>1.090414231015621</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.07337791433219</v>
+        <v>16.56726308813784</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09782587077474333</v>
+        <v>0.09771539337539289</v>
       </c>
       <c r="C14">
-        <v>215.6699671312634</v>
+        <v>213.8223944203485</v>
       </c>
       <c r="D14">
-        <v>236.0999671312634</v>
+        <v>236.6023944203485</v>
       </c>
       <c r="E14">
-        <v>-39.39999999999999</v>
+        <v>-37.05</v>
       </c>
       <c r="F14">
-        <v>28.2</v>
+        <v>30.55</v>
       </c>
       <c r="G14">
         <v>7.77</v>
@@ -2435,28 +2435,28 @@
         <v>23.5</v>
       </c>
       <c r="M14">
-        <v>1.41846</v>
+        <v>1.536665</v>
       </c>
       <c r="N14">
-        <v>22.08154</v>
+        <v>21.963335</v>
       </c>
       <c r="O14">
-        <v>3.312231</v>
+        <v>3.29450025</v>
       </c>
       <c r="P14">
-        <v>18.769309</v>
+        <v>18.66883475</v>
       </c>
       <c r="Q14">
-        <v>25.969309</v>
+        <v>25.86883475</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1053355349712992</v>
+        <v>0.1059278659487275</v>
       </c>
       <c r="T14">
-        <v>1.090414231015621</v>
+        <v>1.101262980885266</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.56726308813784</v>
+        <v>15.29285823520416</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09771539337539289</v>
+        <v>0.09760491597604247</v>
       </c>
       <c r="C15">
-        <v>213.8223944203485</v>
+        <v>211.9769646280819</v>
       </c>
       <c r="D15">
-        <v>236.6023944203485</v>
+        <v>237.1069646280819</v>
       </c>
       <c r="E15">
-        <v>-37.05</v>
+        <v>-34.69999999999999</v>
       </c>
       <c r="F15">
-        <v>30.55</v>
+        <v>32.90000000000001</v>
       </c>
       <c r="G15">
         <v>7.77</v>
@@ -2517,28 +2517,28 @@
         <v>23.5</v>
       </c>
       <c r="M15">
-        <v>1.536665</v>
+        <v>1.65487</v>
       </c>
       <c r="N15">
-        <v>21.963335</v>
+        <v>21.84513</v>
       </c>
       <c r="O15">
-        <v>3.29450025</v>
+        <v>3.2767695</v>
       </c>
       <c r="P15">
-        <v>18.66883475</v>
+        <v>18.5683605</v>
       </c>
       <c r="Q15">
-        <v>25.86883475</v>
+        <v>25.7683605</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1059278659487275</v>
+        <v>0.1065339720651657</v>
       </c>
       <c r="T15">
-        <v>1.101262980885266</v>
+        <v>1.112364027263508</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.29285823520416</v>
+        <v>14.20051121840386</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09760491597604247</v>
+        <v>0.09749443857669206</v>
       </c>
       <c r="C16">
-        <v>211.9769646280819</v>
+        <v>210.133691493509</v>
       </c>
       <c r="D16">
-        <v>237.1069646280819</v>
+        <v>237.613691493509</v>
       </c>
       <c r="E16">
-        <v>-34.69999999999999</v>
+        <v>-32.34999999999999</v>
       </c>
       <c r="F16">
-        <v>32.90000000000001</v>
+        <v>35.25000000000001</v>
       </c>
       <c r="G16">
         <v>7.77</v>
@@ -2599,28 +2599,28 @@
         <v>23.5</v>
       </c>
       <c r="M16">
-        <v>1.65487</v>
+        <v>1.773075</v>
       </c>
       <c r="N16">
-        <v>21.84513</v>
+        <v>21.726925</v>
       </c>
       <c r="O16">
-        <v>3.2767695</v>
+        <v>3.25903875</v>
       </c>
       <c r="P16">
-        <v>18.5683605</v>
+        <v>18.46788625</v>
       </c>
       <c r="Q16">
-        <v>25.7683605</v>
+        <v>25.66788625</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1065339720651657</v>
+        <v>0.1071543395019907</v>
       </c>
       <c r="T16">
-        <v>1.112364027263508</v>
+        <v>1.123726274733002</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.20051121840386</v>
+        <v>13.25381047051027</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09749443857669206</v>
+        <v>0.09758796117734164</v>
       </c>
       <c r="C17">
-        <v>210.133691493509</v>
+        <v>207.3545907937861</v>
       </c>
       <c r="D17">
-        <v>237.613691493509</v>
+        <v>237.184590793786</v>
       </c>
       <c r="E17">
-        <v>-32.34999999999999</v>
+        <v>-29.99999999999999</v>
       </c>
       <c r="F17">
-        <v>35.25</v>
+        <v>37.6</v>
       </c>
       <c r="G17">
         <v>7.77</v>
@@ -2681,45 +2681,45 @@
         <v>23.5</v>
       </c>
       <c r="M17">
-        <v>1.773075</v>
+        <v>1.94768</v>
       </c>
       <c r="N17">
-        <v>21.726925</v>
+        <v>21.55232</v>
       </c>
       <c r="O17">
-        <v>3.25903875</v>
+        <v>3.232848</v>
       </c>
       <c r="P17">
-        <v>18.46788625</v>
+        <v>18.319472</v>
       </c>
       <c r="Q17">
-        <v>25.66788625</v>
+        <v>25.519472</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1071543395019907</v>
+        <v>0.1077894775920734</v>
       </c>
       <c r="T17">
-        <v>1.123726274733002</v>
+        <v>1.135359051904151</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.15</v>
       </c>
       <c r="W17">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.25381047051027</v>
+        <v>12.06563706563707</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09758796117734164</v>
+        <v>0.09749023377799122</v>
       </c>
       <c r="C18">
-        <v>207.3545907937861</v>
+        <v>205.4530204395838</v>
       </c>
       <c r="D18">
-        <v>237.184590793786</v>
+        <v>237.6330204395838</v>
       </c>
       <c r="E18">
-        <v>-29.99999999999999</v>
+        <v>-27.64999999999999</v>
       </c>
       <c r="F18">
-        <v>37.6</v>
+        <v>39.95</v>
       </c>
       <c r="G18">
         <v>7.77</v>
@@ -2763,28 +2763,28 @@
         <v>23.5</v>
       </c>
       <c r="M18">
-        <v>1.94768</v>
+        <v>2.06941</v>
       </c>
       <c r="N18">
-        <v>21.55232</v>
+        <v>21.43059</v>
       </c>
       <c r="O18">
-        <v>3.232848</v>
+        <v>3.2145885</v>
       </c>
       <c r="P18">
-        <v>18.319472</v>
+        <v>18.2160015</v>
       </c>
       <c r="Q18">
-        <v>25.519472</v>
+        <v>25.4160015</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1077894775920734</v>
+        <v>0.1084399202144473</v>
       </c>
       <c r="T18">
-        <v>1.135359051904151</v>
+        <v>1.147272136958942</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.06563706563707</v>
+        <v>11.35589370883488</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09749023377799122</v>
+        <v>0.0973925063786408</v>
       </c>
       <c r="C19">
-        <v>205.4530204395838</v>
+        <v>203.5531489314409</v>
       </c>
       <c r="D19">
-        <v>237.6330204395838</v>
+        <v>238.0831489314409</v>
       </c>
       <c r="E19">
-        <v>-27.64999999999999</v>
+        <v>-25.29999999999999</v>
       </c>
       <c r="F19">
-        <v>39.95</v>
+        <v>42.3</v>
       </c>
       <c r="G19">
         <v>7.77</v>
@@ -2845,28 +2845,28 @@
         <v>23.5</v>
       </c>
       <c r="M19">
-        <v>2.06941</v>
+        <v>2.19114</v>
       </c>
       <c r="N19">
-        <v>21.43059</v>
+        <v>21.30886</v>
       </c>
       <c r="O19">
-        <v>3.2145885</v>
+        <v>3.196329</v>
       </c>
       <c r="P19">
-        <v>18.2160015</v>
+        <v>18.112531</v>
       </c>
       <c r="Q19">
-        <v>25.4160015</v>
+        <v>25.312531</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1084399202144473</v>
+        <v>0.1091062272910254</v>
       </c>
       <c r="T19">
-        <v>1.147272136958942</v>
+        <v>1.159475785063851</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.35589370883488</v>
+        <v>10.72501072501072</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0973925063786408</v>
+        <v>0.09729477897929037</v>
       </c>
       <c r="C20">
-        <v>203.5531489314409</v>
+        <v>201.6549859416277</v>
       </c>
       <c r="D20">
-        <v>238.0831489314409</v>
+        <v>238.5349859416277</v>
       </c>
       <c r="E20">
-        <v>-25.3</v>
+        <v>-22.95</v>
       </c>
       <c r="F20">
-        <v>42.3</v>
+        <v>44.65</v>
       </c>
       <c r="G20">
         <v>7.77</v>
@@ -2927,28 +2927,28 @@
         <v>23.5</v>
       </c>
       <c r="M20">
-        <v>2.19114</v>
+        <v>2.31287</v>
       </c>
       <c r="N20">
-        <v>21.30886</v>
+        <v>21.18713</v>
       </c>
       <c r="O20">
-        <v>3.196329</v>
+        <v>3.1780695</v>
       </c>
       <c r="P20">
-        <v>18.112531</v>
+        <v>18.0090605</v>
       </c>
       <c r="Q20">
-        <v>25.312531</v>
+        <v>25.2090605</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1091062272910254</v>
+        <v>0.1097889863941856</v>
       </c>
       <c r="T20">
-        <v>1.159475785063851</v>
+        <v>1.171980757813324</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.72501072501072</v>
+        <v>10.16053647632595</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09729477897929037</v>
+        <v>0.09748605157993995</v>
       </c>
       <c r="C21">
-        <v>201.6549859416277</v>
+        <v>198.4222486128457</v>
       </c>
       <c r="D21">
-        <v>238.5349859416277</v>
+        <v>237.6522486128457</v>
       </c>
       <c r="E21">
-        <v>-22.95</v>
+        <v>-20.59999999999999</v>
       </c>
       <c r="F21">
-        <v>44.65</v>
+        <v>47</v>
       </c>
       <c r="G21">
         <v>7.77</v>
@@ -3009,45 +3009,45 @@
         <v>23.5</v>
       </c>
       <c r="M21">
-        <v>2.31287</v>
+        <v>2.5145</v>
       </c>
       <c r="N21">
-        <v>21.18713</v>
+        <v>20.9855</v>
       </c>
       <c r="O21">
-        <v>3.1780695</v>
+        <v>3.147825</v>
       </c>
       <c r="P21">
-        <v>18.0090605</v>
+        <v>17.837675</v>
       </c>
       <c r="Q21">
-        <v>25.2090605</v>
+        <v>25.037675</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1097889863941856</v>
+        <v>0.1104888144749249</v>
       </c>
       <c r="T21">
-        <v>1.171980757813324</v>
+        <v>1.184798354881535</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.15</v>
       </c>
       <c r="W21">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>10.16053647632595</v>
+        <v>9.345794392523365</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09748605157993995</v>
+        <v>0.09740277418058953</v>
       </c>
       <c r="C22">
-        <v>198.4222486128457</v>
+        <v>196.4557756911574</v>
       </c>
       <c r="D22">
-        <v>237.6522486128457</v>
+        <v>238.0357756911574</v>
       </c>
       <c r="E22">
-        <v>-20.59999999999999</v>
+        <v>-18.24999999999999</v>
       </c>
       <c r="F22">
-        <v>47</v>
+        <v>49.35</v>
       </c>
       <c r="G22">
         <v>7.77</v>
@@ -3091,28 +3091,28 @@
         <v>23.5</v>
       </c>
       <c r="M22">
-        <v>2.5145</v>
+        <v>2.640225</v>
       </c>
       <c r="N22">
-        <v>20.9855</v>
+        <v>20.859775</v>
       </c>
       <c r="O22">
-        <v>3.147825</v>
+        <v>3.12896625</v>
       </c>
       <c r="P22">
-        <v>17.837675</v>
+        <v>17.73080875</v>
       </c>
       <c r="Q22">
-        <v>25.037675</v>
+        <v>24.93080875</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1104888144749249</v>
+        <v>0.1112063597222652</v>
       </c>
       <c r="T22">
-        <v>1.184798354881535</v>
+        <v>1.197940448078055</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.345794392523365</v>
+        <v>8.900756564307965</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09740277418058953</v>
+        <v>0.09731949678123911</v>
       </c>
       <c r="C23">
-        <v>196.4557756911574</v>
+        <v>194.490542654936</v>
       </c>
       <c r="D23">
-        <v>238.0357756911574</v>
+        <v>238.420542654936</v>
       </c>
       <c r="E23">
-        <v>-18.24999999999999</v>
+        <v>-15.89999999999999</v>
       </c>
       <c r="F23">
-        <v>49.35</v>
+        <v>51.7</v>
       </c>
       <c r="G23">
         <v>7.77</v>
@@ -3173,28 +3173,28 @@
         <v>23.5</v>
       </c>
       <c r="M23">
-        <v>2.640225</v>
+        <v>2.76595</v>
       </c>
       <c r="N23">
-        <v>20.859775</v>
+        <v>20.73405</v>
       </c>
       <c r="O23">
-        <v>3.12896625</v>
+        <v>3.1101075</v>
       </c>
       <c r="P23">
-        <v>17.73080875</v>
+        <v>17.6239425</v>
       </c>
       <c r="Q23">
-        <v>24.93080875</v>
+        <v>24.8239425</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1112063597222652</v>
+        <v>0.1119423035656912</v>
       </c>
       <c r="T23">
-        <v>1.197940448078054</v>
+        <v>1.211419518023203</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.900756564307965</v>
+        <v>8.496176720475786</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09731949678123911</v>
+        <v>0.09723621938188869</v>
       </c>
       <c r="C24">
-        <v>194.490542654936</v>
+        <v>192.5265555264615</v>
       </c>
       <c r="D24">
-        <v>238.420542654936</v>
+        <v>238.8065555264615</v>
       </c>
       <c r="E24">
-        <v>-15.89999999999999</v>
+        <v>-13.54999999999999</v>
       </c>
       <c r="F24">
-        <v>51.7</v>
+        <v>54.05</v>
       </c>
       <c r="G24">
         <v>7.77</v>
@@ -3255,28 +3255,28 @@
         <v>23.5</v>
       </c>
       <c r="M24">
-        <v>2.76595</v>
+        <v>2.891675</v>
       </c>
       <c r="N24">
-        <v>20.73405</v>
+        <v>20.608325</v>
       </c>
       <c r="O24">
-        <v>3.1101075</v>
+        <v>3.09124875</v>
       </c>
       <c r="P24">
-        <v>17.6239425</v>
+        <v>17.51707625</v>
       </c>
       <c r="Q24">
-        <v>24.8239425</v>
+        <v>24.71707625</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1119423035656912</v>
+        <v>0.1126973628336217</v>
       </c>
       <c r="T24">
-        <v>1.211419518023203</v>
+        <v>1.225248693681212</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.496176720475786</v>
+        <v>8.126777732629012</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09723621938188869</v>
+        <v>0.09715294198253827</v>
       </c>
       <c r="C25">
-        <v>192.5265555264615</v>
+        <v>190.5638203670783</v>
       </c>
       <c r="D25">
-        <v>238.8065555264615</v>
+        <v>239.1938203670783</v>
       </c>
       <c r="E25">
-        <v>-13.54999999999999</v>
+        <v>-11.19999999999999</v>
       </c>
       <c r="F25">
-        <v>54.05</v>
+        <v>56.40000000000001</v>
       </c>
       <c r="G25">
         <v>7.77</v>
@@ -3337,28 +3337,28 @@
         <v>23.5</v>
       </c>
       <c r="M25">
-        <v>2.891675</v>
+        <v>3.0174</v>
       </c>
       <c r="N25">
-        <v>20.608325</v>
+        <v>20.4826</v>
       </c>
       <c r="O25">
-        <v>3.09124875</v>
+        <v>3.07239</v>
       </c>
       <c r="P25">
-        <v>17.51707625</v>
+        <v>17.41021</v>
       </c>
       <c r="Q25">
-        <v>24.71707625</v>
+        <v>24.61021</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1126973628336217</v>
+        <v>0.1134722920822872</v>
       </c>
       <c r="T25">
-        <v>1.225248693681212</v>
+        <v>1.239441795014433</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.126777732629012</v>
+        <v>7.788161993769469</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09715294198253825</v>
+        <v>0.09723966458318785</v>
       </c>
       <c r="C26">
-        <v>190.5638203670784</v>
+        <v>187.8105613192283</v>
       </c>
       <c r="D26">
-        <v>239.1938203670784</v>
+        <v>238.7905613192283</v>
       </c>
       <c r="E26">
-        <v>-11.2</v>
+        <v>-8.849999999999994</v>
       </c>
       <c r="F26">
-        <v>56.4</v>
+        <v>58.75</v>
       </c>
       <c r="G26">
         <v>7.77</v>
@@ -3419,45 +3419,45 @@
         <v>23.5</v>
       </c>
       <c r="M26">
-        <v>3.0174</v>
+        <v>3.190125</v>
       </c>
       <c r="N26">
-        <v>20.4826</v>
+        <v>20.309875</v>
       </c>
       <c r="O26">
-        <v>3.07239</v>
+        <v>3.04648125</v>
       </c>
       <c r="P26">
-        <v>17.41021</v>
+        <v>17.26339375</v>
       </c>
       <c r="Q26">
-        <v>24.61021</v>
+        <v>24.46339375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1134722920822872</v>
+        <v>0.1142678861109171</v>
       </c>
       <c r="T26">
-        <v>1.239441795014433</v>
+        <v>1.254013379049872</v>
       </c>
       <c r="U26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.15</v>
       </c>
       <c r="W26">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.788161993769471</v>
+        <v>7.366482504604051</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09723966458318785</v>
+        <v>0.09716318718383742</v>
       </c>
       <c r="C27">
-        <v>187.8105613192283</v>
+        <v>185.8161093706715</v>
       </c>
       <c r="D27">
-        <v>238.7905613192283</v>
+        <v>239.1461093706715</v>
       </c>
       <c r="E27">
-        <v>-8.849999999999994</v>
+        <v>-6.499999999999993</v>
       </c>
       <c r="F27">
-        <v>58.75</v>
+        <v>61.1</v>
       </c>
       <c r="G27">
         <v>7.77</v>
@@ -3501,28 +3501,28 @@
         <v>23.5</v>
       </c>
       <c r="M27">
-        <v>3.190125</v>
+        <v>3.31773</v>
       </c>
       <c r="N27">
-        <v>20.309875</v>
+        <v>20.18227</v>
       </c>
       <c r="O27">
-        <v>3.04648125</v>
+        <v>3.0273405</v>
       </c>
       <c r="P27">
-        <v>17.26339375</v>
+        <v>17.1549295</v>
       </c>
       <c r="Q27">
-        <v>24.46339375</v>
+        <v>24.3549295</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1142678861109171</v>
+        <v>0.1150849826808614</v>
       </c>
       <c r="T27">
-        <v>1.254013379049872</v>
+        <v>1.268978789680864</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.366482504604051</v>
+        <v>7.083156254426973</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09716318718383742</v>
+        <v>0.097086709784487</v>
       </c>
       <c r="C28">
-        <v>185.8161093706715</v>
+        <v>183.8227177900123</v>
       </c>
       <c r="D28">
-        <v>239.1461093706715</v>
+        <v>239.5027177900124</v>
       </c>
       <c r="E28">
-        <v>-6.499999999999993</v>
+        <v>-4.149999999999991</v>
       </c>
       <c r="F28">
-        <v>61.1</v>
+        <v>63.45</v>
       </c>
       <c r="G28">
         <v>7.77</v>
@@ -3583,28 +3583,28 @@
         <v>23.5</v>
       </c>
       <c r="M28">
-        <v>3.31773</v>
+        <v>3.445335</v>
       </c>
       <c r="N28">
-        <v>20.18227</v>
+        <v>20.054665</v>
       </c>
       <c r="O28">
-        <v>3.0273405</v>
+        <v>3.00819975</v>
       </c>
       <c r="P28">
-        <v>17.1549295</v>
+        <v>17.04646525</v>
       </c>
       <c r="Q28">
-        <v>24.3549295</v>
+        <v>24.24646525</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1150849826808614</v>
+        <v>0.1159244654582014</v>
       </c>
       <c r="T28">
-        <v>1.268978789680864</v>
+        <v>1.28435421156202</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.083156254426973</v>
+        <v>6.82081713389264</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.097086709784487</v>
+        <v>0.09701023238513658</v>
       </c>
       <c r="C29">
-        <v>183.8227177900123</v>
+        <v>181.8303913279136</v>
       </c>
       <c r="D29">
-        <v>239.5027177900124</v>
+        <v>239.8603913279136</v>
       </c>
       <c r="E29">
-        <v>-4.149999999999991</v>
+        <v>-1.799999999999983</v>
       </c>
       <c r="F29">
-        <v>63.45</v>
+        <v>65.80000000000001</v>
       </c>
       <c r="G29">
         <v>7.77</v>
@@ -3665,28 +3665,28 @@
         <v>23.5</v>
       </c>
       <c r="M29">
-        <v>3.445335</v>
+        <v>3.572940000000001</v>
       </c>
       <c r="N29">
-        <v>20.054665</v>
+        <v>19.92706</v>
       </c>
       <c r="O29">
-        <v>3.00819975</v>
+        <v>2.989059</v>
       </c>
       <c r="P29">
-        <v>17.04646525</v>
+        <v>16.938001</v>
       </c>
       <c r="Q29">
-        <v>24.24646525</v>
+        <v>24.138001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1159244654582014</v>
+        <v>0.1167872672015786</v>
       </c>
       <c r="T29">
-        <v>1.28435421156202</v>
+        <v>1.30015672849543</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.82081713389264</v>
+        <v>6.577216521967901</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09701023238513658</v>
+        <v>0.09693375498578616</v>
       </c>
       <c r="C30">
-        <v>181.8303913279136</v>
+        <v>179.839134763459</v>
       </c>
       <c r="D30">
-        <v>239.8603913279136</v>
+        <v>240.219134763459</v>
       </c>
       <c r="E30">
-        <v>-1.799999999999983</v>
+        <v>0.5500000000000114</v>
       </c>
       <c r="F30">
-        <v>65.80000000000001</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="G30">
         <v>7.77</v>
@@ -3747,28 +3747,28 @@
         <v>23.5</v>
       </c>
       <c r="M30">
-        <v>3.572940000000001</v>
+        <v>3.700545</v>
       </c>
       <c r="N30">
-        <v>19.92706</v>
+        <v>19.799455</v>
       </c>
       <c r="O30">
-        <v>2.989059</v>
+        <v>2.96991825</v>
       </c>
       <c r="P30">
-        <v>16.938001</v>
+        <v>16.82953675</v>
       </c>
       <c r="Q30">
-        <v>24.138001</v>
+        <v>24.02953675</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1167872672015786</v>
+        <v>0.1176743732194171</v>
       </c>
       <c r="T30">
-        <v>1.30015672849543</v>
+        <v>1.316404386750908</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.577216521967901</v>
+        <v>6.350415952244871</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09693375498578616</v>
+        <v>0.09685727758643572</v>
       </c>
       <c r="C31">
-        <v>179.839134763459</v>
+        <v>177.8489529043659</v>
       </c>
       <c r="D31">
-        <v>240.219134763459</v>
+        <v>240.5789529043659</v>
       </c>
       <c r="E31">
-        <v>0.5499999999999972</v>
+        <v>2.900000000000006</v>
       </c>
       <c r="F31">
-        <v>68.14999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="G31">
         <v>7.77</v>
@@ -3829,28 +3829,28 @@
         <v>23.5</v>
       </c>
       <c r="M31">
-        <v>3.700545</v>
+        <v>3.82815</v>
       </c>
       <c r="N31">
-        <v>19.799455</v>
+        <v>19.67185</v>
       </c>
       <c r="O31">
-        <v>2.96991825</v>
+        <v>2.9507775</v>
       </c>
       <c r="P31">
-        <v>16.82953675</v>
+        <v>16.7210725</v>
       </c>
       <c r="Q31">
-        <v>24.02953675</v>
+        <v>23.9210725</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1176743732194171</v>
+        <v>0.1185868251234796</v>
       </c>
       <c r="T31">
-        <v>1.316404386750908</v>
+        <v>1.333116263813686</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.350415952244873</v>
+        <v>6.138735420503376</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09685727758643572</v>
+        <v>0.09704430018708531</v>
       </c>
       <c r="C32">
-        <v>177.8489529043659</v>
+        <v>174.6209293725885</v>
       </c>
       <c r="D32">
-        <v>240.5789529043659</v>
+        <v>239.7009293725885</v>
       </c>
       <c r="E32">
-        <v>2.900000000000006</v>
+        <v>5.25</v>
       </c>
       <c r="F32">
-        <v>70.5</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="G32">
         <v>7.77</v>
@@ -3911,45 +3911,45 @@
         <v>23.5</v>
       </c>
       <c r="M32">
-        <v>3.82815</v>
+        <v>4.028605</v>
       </c>
       <c r="N32">
-        <v>19.67185</v>
+        <v>19.471395</v>
       </c>
       <c r="O32">
-        <v>2.9507775</v>
+        <v>2.92070925</v>
       </c>
       <c r="P32">
-        <v>16.7210725</v>
+        <v>16.55068575</v>
       </c>
       <c r="Q32">
-        <v>23.9210725</v>
+        <v>23.75068575</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1185868251234796</v>
+        <v>0.1195257249088193</v>
       </c>
       <c r="T32">
-        <v>1.333116263813686</v>
+        <v>1.350312543110167</v>
       </c>
       <c r="U32">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V32">
         <v>0.15</v>
       </c>
       <c r="W32">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>6.138735420503376</v>
+        <v>5.833284722627312</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09704430018708531</v>
+        <v>0.09697632278773487</v>
       </c>
       <c r="C33">
-        <v>174.6209293725885</v>
+        <v>172.5893236008767</v>
       </c>
       <c r="D33">
-        <v>239.7009293725885</v>
+        <v>240.0193236008767</v>
       </c>
       <c r="E33">
-        <v>5.25</v>
+        <v>7.600000000000009</v>
       </c>
       <c r="F33">
-        <v>72.84999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="G33">
         <v>7.77</v>
@@ -3993,28 +3993,28 @@
         <v>23.5</v>
       </c>
       <c r="M33">
-        <v>4.028605</v>
+        <v>4.15856</v>
       </c>
       <c r="N33">
-        <v>19.471395</v>
+        <v>19.34144</v>
       </c>
       <c r="O33">
-        <v>2.92070925</v>
+        <v>2.901216</v>
       </c>
       <c r="P33">
-        <v>16.55068575</v>
+        <v>16.440224</v>
       </c>
       <c r="Q33">
-        <v>23.75068575</v>
+        <v>23.640224</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1195257249088193</v>
+        <v>0.1204922393937277</v>
       </c>
       <c r="T33">
-        <v>1.350312543110167</v>
+        <v>1.368014595327133</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.833284722627312</v>
+        <v>5.650994575045207</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09697632278773487</v>
+        <v>0.09690834538838444</v>
       </c>
       <c r="C34">
-        <v>172.5893236008767</v>
+        <v>170.5585647989286</v>
       </c>
       <c r="D34">
-        <v>240.0193236008767</v>
+        <v>240.3385647989285</v>
       </c>
       <c r="E34">
-        <v>7.600000000000009</v>
+        <v>9.950000000000003</v>
       </c>
       <c r="F34">
-        <v>75.2</v>
+        <v>77.55</v>
       </c>
       <c r="G34">
         <v>7.77</v>
@@ -4075,28 +4075,28 @@
         <v>23.5</v>
       </c>
       <c r="M34">
-        <v>4.15856</v>
+        <v>4.288515</v>
       </c>
       <c r="N34">
-        <v>19.34144</v>
+        <v>19.211485</v>
       </c>
       <c r="O34">
-        <v>2.901216</v>
+        <v>2.88172275</v>
       </c>
       <c r="P34">
-        <v>16.440224</v>
+        <v>16.32976225</v>
       </c>
       <c r="Q34">
-        <v>23.640224</v>
+        <v>23.52976225</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1204922393937277</v>
+        <v>0.1214876050572902</v>
       </c>
       <c r="T34">
-        <v>1.368014595327133</v>
+        <v>1.386245067013262</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.650994575045207</v>
+        <v>5.479752315195353</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09690834538838444</v>
+        <v>0.09684036798903402</v>
       </c>
       <c r="C35">
-        <v>170.5585647989286</v>
+        <v>168.5286563508185</v>
       </c>
       <c r="D35">
-        <v>240.3385647989285</v>
+        <v>240.6586563508185</v>
       </c>
       <c r="E35">
-        <v>9.950000000000003</v>
+        <v>12.30000000000001</v>
       </c>
       <c r="F35">
-        <v>77.55</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="G35">
         <v>7.77</v>
@@ -4157,28 +4157,28 @@
         <v>23.5</v>
       </c>
       <c r="M35">
-        <v>4.288515</v>
+        <v>4.41847</v>
       </c>
       <c r="N35">
-        <v>19.211485</v>
+        <v>19.08153</v>
       </c>
       <c r="O35">
-        <v>2.88172275</v>
+        <v>2.8622295</v>
       </c>
       <c r="P35">
-        <v>16.32976225</v>
+        <v>16.2193005</v>
       </c>
       <c r="Q35">
-        <v>23.52976225</v>
+        <v>23.4193005</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1214876050572902</v>
+        <v>0.1225131333167182</v>
       </c>
       <c r="T35">
-        <v>1.386245067013262</v>
+        <v>1.405027977235335</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.479752315195353</v>
+        <v>5.318583129454313</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09684036798903402</v>
+        <v>0.09677239058968361</v>
       </c>
       <c r="C36">
-        <v>168.5286563508185</v>
+        <v>166.4996016586732</v>
       </c>
       <c r="D36">
-        <v>240.6586563508185</v>
+        <v>240.9796016586731</v>
       </c>
       <c r="E36">
-        <v>12.30000000000001</v>
+        <v>14.65000000000002</v>
       </c>
       <c r="F36">
-        <v>79.90000000000001</v>
+        <v>82.25000000000001</v>
       </c>
       <c r="G36">
         <v>7.77</v>
@@ -4239,28 +4239,28 @@
         <v>23.5</v>
       </c>
       <c r="M36">
-        <v>4.41847</v>
+        <v>4.548425000000001</v>
       </c>
       <c r="N36">
-        <v>19.08153</v>
+        <v>18.951575</v>
       </c>
       <c r="O36">
-        <v>2.8622295</v>
+        <v>2.84273625</v>
       </c>
       <c r="P36">
-        <v>16.2193005</v>
+        <v>16.10883875</v>
       </c>
       <c r="Q36">
-        <v>23.4193005</v>
+        <v>23.30883875</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1225131333167182</v>
+        <v>0.1235702162918209</v>
       </c>
       <c r="T36">
-        <v>1.405027977235335</v>
+        <v>1.424388823156548</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.318583129454313</v>
+        <v>5.166623611469904</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09677239058968361</v>
+        <v>0.0967044131903332</v>
       </c>
       <c r="C37">
-        <v>166.4996016586732</v>
+        <v>164.4714041427919</v>
       </c>
       <c r="D37">
-        <v>240.9796016586731</v>
+        <v>241.3014041427919</v>
       </c>
       <c r="E37">
-        <v>14.65000000000002</v>
+        <v>17.00000000000001</v>
       </c>
       <c r="F37">
-        <v>82.25000000000001</v>
+        <v>84.60000000000001</v>
       </c>
       <c r="G37">
         <v>7.77</v>
@@ -4321,28 +4321,28 @@
         <v>23.5</v>
       </c>
       <c r="M37">
-        <v>4.548425000000001</v>
+        <v>4.678380000000001</v>
       </c>
       <c r="N37">
-        <v>18.951575</v>
+        <v>18.82162</v>
       </c>
       <c r="O37">
-        <v>2.84273625</v>
+        <v>2.823243</v>
       </c>
       <c r="P37">
-        <v>16.10883875</v>
+        <v>15.998377</v>
       </c>
       <c r="Q37">
-        <v>23.30883875</v>
+        <v>23.198377</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1235702162918209</v>
+        <v>0.1246603331098956</v>
       </c>
       <c r="T37">
-        <v>1.424388823156548</v>
+        <v>1.444354695512799</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.166623611469904</v>
+        <v>5.023106288929073</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09670441319033318</v>
+        <v>0.09663643579098277</v>
       </c>
       <c r="C38">
-        <v>164.4714041427919</v>
+        <v>162.4440672417682</v>
       </c>
       <c r="D38">
-        <v>241.3014041427919</v>
+        <v>241.6240672417682</v>
       </c>
       <c r="E38">
-        <v>17</v>
+        <v>19.35000000000001</v>
       </c>
       <c r="F38">
-        <v>84.59999999999999</v>
+        <v>86.95</v>
       </c>
       <c r="G38">
         <v>7.77</v>
@@ -4403,28 +4403,28 @@
         <v>23.5</v>
       </c>
       <c r="M38">
-        <v>4.67838</v>
+        <v>4.808335</v>
       </c>
       <c r="N38">
-        <v>18.82162</v>
+        <v>18.691665</v>
       </c>
       <c r="O38">
-        <v>2.823243</v>
+        <v>2.80374975</v>
       </c>
       <c r="P38">
-        <v>15.998377</v>
+        <v>15.88791525</v>
       </c>
       <c r="Q38">
-        <v>23.198377</v>
+        <v>23.08791525</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1246603331098956</v>
+        <v>0.1257850568110838</v>
       </c>
       <c r="T38">
-        <v>1.444354695512799</v>
+        <v>1.464954405086709</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.023106288929074</v>
+        <v>4.887346659498558</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09663643579098277</v>
+        <v>0.09656845839163235</v>
       </c>
       <c r="C39">
-        <v>162.4440672417682</v>
+        <v>160.4175944126125</v>
       </c>
       <c r="D39">
-        <v>241.6240672417682</v>
+        <v>241.9475944126125</v>
       </c>
       <c r="E39">
-        <v>19.35000000000001</v>
+        <v>21.7</v>
       </c>
       <c r="F39">
-        <v>86.95</v>
+        <v>89.3</v>
       </c>
       <c r="G39">
         <v>7.77</v>
@@ -4485,28 +4485,28 @@
         <v>23.5</v>
       </c>
       <c r="M39">
-        <v>4.808335</v>
+        <v>4.93829</v>
       </c>
       <c r="N39">
-        <v>18.691665</v>
+        <v>18.56171</v>
       </c>
       <c r="O39">
-        <v>2.80374975</v>
+        <v>2.7842565</v>
       </c>
       <c r="P39">
-        <v>15.88791525</v>
+        <v>15.7774535</v>
       </c>
       <c r="Q39">
-        <v>23.08791525</v>
+        <v>22.9774535</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1257850568110838</v>
+        <v>0.1269460619219877</v>
       </c>
       <c r="T39">
-        <v>1.464954405086709</v>
+        <v>1.486218621421068</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.887346659498558</v>
+        <v>4.75873227372228</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09656845839163235</v>
+        <v>0.09650048099228191</v>
       </c>
       <c r="C40">
-        <v>160.4175944126125</v>
+        <v>158.3919891308749</v>
       </c>
       <c r="D40">
-        <v>241.9475944126125</v>
+        <v>242.2719891308749</v>
       </c>
       <c r="E40">
-        <v>21.7</v>
+        <v>24.05000000000001</v>
       </c>
       <c r="F40">
-        <v>89.3</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="G40">
         <v>7.77</v>
@@ -4567,28 +4567,28 @@
         <v>23.5</v>
       </c>
       <c r="M40">
-        <v>4.93829</v>
+        <v>5.068245</v>
       </c>
       <c r="N40">
-        <v>18.56171</v>
+        <v>18.431755</v>
       </c>
       <c r="O40">
-        <v>2.7842565</v>
+        <v>2.76476325</v>
       </c>
       <c r="P40">
-        <v>15.7774535</v>
+        <v>15.66699175</v>
       </c>
       <c r="Q40">
-        <v>22.9774535</v>
+        <v>22.86699175</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1269460619219877</v>
+        <v>0.1281451327742326</v>
       </c>
       <c r="T40">
-        <v>1.486218621421068</v>
+        <v>1.508180025176225</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.75873227372228</v>
+        <v>4.636713497472991</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09650048099228191</v>
+        <v>0.0964325035929315</v>
       </c>
       <c r="C41">
-        <v>158.3919891308749</v>
+        <v>156.3672548907705</v>
       </c>
       <c r="D41">
-        <v>242.2719891308749</v>
+        <v>242.5972548907705</v>
       </c>
       <c r="E41">
-        <v>24.05000000000001</v>
+        <v>26.40000000000001</v>
       </c>
       <c r="F41">
-        <v>91.65000000000001</v>
+        <v>94</v>
       </c>
       <c r="G41">
         <v>7.77</v>
@@ -4649,28 +4649,28 @@
         <v>23.5</v>
       </c>
       <c r="M41">
-        <v>5.068245</v>
+        <v>5.1982</v>
       </c>
       <c r="N41">
-        <v>18.431755</v>
+        <v>18.3018</v>
       </c>
       <c r="O41">
-        <v>2.76476325</v>
+        <v>2.74527</v>
       </c>
       <c r="P41">
-        <v>15.66699175</v>
+        <v>15.55653</v>
       </c>
       <c r="Q41">
-        <v>22.86699175</v>
+        <v>22.75653</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1281451327742326</v>
+        <v>0.1293841726548858</v>
       </c>
       <c r="T41">
-        <v>1.508180025176225</v>
+        <v>1.530873475723221</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.636713497472991</v>
+        <v>4.520795660036166</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0964325035929315</v>
+        <v>0.09723577619358108</v>
       </c>
       <c r="C42">
-        <v>156.3672548907705</v>
+        <v>150.2286131657356</v>
       </c>
       <c r="D42">
-        <v>242.5972548907705</v>
+        <v>238.8086131657356</v>
       </c>
       <c r="E42">
-        <v>26.40000000000001</v>
+        <v>28.75000000000001</v>
       </c>
       <c r="F42">
-        <v>94</v>
+        <v>96.35000000000001</v>
       </c>
       <c r="G42">
         <v>7.77</v>
@@ -4731,45 +4731,45 @@
         <v>23.5</v>
       </c>
       <c r="M42">
-        <v>5.1982</v>
+        <v>5.569030000000001</v>
       </c>
       <c r="N42">
-        <v>18.3018</v>
+        <v>17.93097</v>
       </c>
       <c r="O42">
-        <v>2.74527</v>
+        <v>2.6896455</v>
       </c>
       <c r="P42">
-        <v>15.55653</v>
+        <v>15.2413245</v>
       </c>
       <c r="Q42">
-        <v>22.75653</v>
+        <v>22.4413245</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1293841726548858</v>
+        <v>0.1306652138874256</v>
       </c>
       <c r="T42">
-        <v>1.530873475723221</v>
+        <v>1.554336195780284</v>
       </c>
       <c r="U42">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V42">
         <v>0.15</v>
       </c>
       <c r="W42">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.520795660036166</v>
+        <v>4.219765381044813</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09723577619358108</v>
+        <v>0.09718904879423065</v>
       </c>
       <c r="C43">
-        <v>150.2286131657356</v>
+        <v>148.0957587579881</v>
       </c>
       <c r="D43">
-        <v>238.8086131657356</v>
+        <v>239.0257587579881</v>
       </c>
       <c r="E43">
-        <v>28.75000000000001</v>
+        <v>31.10000000000001</v>
       </c>
       <c r="F43">
-        <v>96.35000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="G43">
         <v>7.77</v>
@@ -4813,28 +4813,28 @@
         <v>23.5</v>
       </c>
       <c r="M43">
-        <v>5.569030000000001</v>
+        <v>5.704860000000001</v>
       </c>
       <c r="N43">
-        <v>17.93097</v>
+        <v>17.79514</v>
       </c>
       <c r="O43">
-        <v>2.6896455</v>
+        <v>2.669271</v>
       </c>
       <c r="P43">
-        <v>15.2413245</v>
+        <v>15.125869</v>
       </c>
       <c r="Q43">
-        <v>22.4413245</v>
+        <v>22.325869</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1306652138874256</v>
+        <v>0.1319904289555701</v>
       </c>
       <c r="T43">
-        <v>1.554336195780284</v>
+        <v>1.57860797514966</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.219765381044813</v>
+        <v>4.119294776734223</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09718904879423067</v>
+        <v>0.09714232139488024</v>
       </c>
       <c r="C44">
-        <v>148.0957587579881</v>
+        <v>145.963299605014</v>
       </c>
       <c r="D44">
-        <v>239.025758757988</v>
+        <v>239.243299605014</v>
       </c>
       <c r="E44">
-        <v>31.10000000000001</v>
+        <v>33.45</v>
       </c>
       <c r="F44">
-        <v>98.7</v>
+        <v>101.05</v>
       </c>
       <c r="G44">
         <v>7.77</v>
@@ -4895,28 +4895,28 @@
         <v>23.5</v>
       </c>
       <c r="M44">
-        <v>5.704860000000001</v>
+        <v>5.84069</v>
       </c>
       <c r="N44">
-        <v>17.79514</v>
+        <v>17.65931</v>
       </c>
       <c r="O44">
-        <v>2.669271</v>
+        <v>2.6488965</v>
       </c>
       <c r="P44">
-        <v>15.125869</v>
+        <v>15.0104135</v>
       </c>
       <c r="Q44">
-        <v>22.325869</v>
+        <v>22.2104135</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1319904289555701</v>
+        <v>0.1333621427980355</v>
       </c>
       <c r="T44">
-        <v>1.57860797514966</v>
+        <v>1.603731395900417</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.119294776734223</v>
+        <v>4.023497223786915</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09714232139488024</v>
+        <v>0.09840459399552981</v>
       </c>
       <c r="C45">
-        <v>145.963299605014</v>
+        <v>137.8725412597245</v>
       </c>
       <c r="D45">
-        <v>239.243299605014</v>
+        <v>233.5025412597245</v>
       </c>
       <c r="E45">
-        <v>33.45</v>
+        <v>35.80000000000001</v>
       </c>
       <c r="F45">
-        <v>101.05</v>
+        <v>103.4</v>
       </c>
       <c r="G45">
         <v>7.77</v>
@@ -4977,45 +4977,45 @@
         <v>23.5</v>
       </c>
       <c r="M45">
-        <v>5.84069</v>
+        <v>6.33842</v>
       </c>
       <c r="N45">
-        <v>17.65931</v>
+        <v>17.16158</v>
       </c>
       <c r="O45">
-        <v>2.6488965</v>
+        <v>2.574237</v>
       </c>
       <c r="P45">
-        <v>15.0104135</v>
+        <v>14.587343</v>
       </c>
       <c r="Q45">
-        <v>22.2104135</v>
+        <v>21.787343</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1333621427980355</v>
+        <v>0.1347828464205889</v>
       </c>
       <c r="T45">
-        <v>1.603731395900417</v>
+        <v>1.629752081677988</v>
       </c>
       <c r="U45">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V45">
         <v>0.15</v>
       </c>
       <c r="W45">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.023497223786915</v>
+        <v>3.707548568886252</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09840459399552981</v>
+        <v>0.09838761659617939</v>
       </c>
       <c r="C46">
-        <v>137.8725412597245</v>
+        <v>135.597925278794</v>
       </c>
       <c r="D46">
-        <v>233.5025412597245</v>
+        <v>233.5779252787939</v>
       </c>
       <c r="E46">
-        <v>35.80000000000001</v>
+        <v>38.15000000000001</v>
       </c>
       <c r="F46">
-        <v>103.4</v>
+        <v>105.75</v>
       </c>
       <c r="G46">
         <v>7.77</v>
@@ -5059,28 +5059,28 @@
         <v>23.5</v>
       </c>
       <c r="M46">
-        <v>6.33842</v>
+        <v>6.482475</v>
       </c>
       <c r="N46">
-        <v>17.16158</v>
+        <v>17.017525</v>
       </c>
       <c r="O46">
-        <v>2.574237</v>
+        <v>2.55262875</v>
       </c>
       <c r="P46">
-        <v>14.587343</v>
+        <v>14.46489625</v>
       </c>
       <c r="Q46">
-        <v>21.787343</v>
+        <v>21.66489625</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1347828464205889</v>
+        <v>0.1362552119930534</v>
       </c>
       <c r="T46">
-        <v>1.629752081677988</v>
+        <v>1.656718974211106</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.707548568886252</v>
+        <v>3.62515860068878</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09838761659617939</v>
+        <v>0.09837063919682897</v>
       </c>
       <c r="C47">
-        <v>135.597925278794</v>
+        <v>133.3233579875738</v>
       </c>
       <c r="D47">
-        <v>233.5779252787939</v>
+        <v>233.6533579875738</v>
       </c>
       <c r="E47">
-        <v>38.15000000000001</v>
+        <v>40.50000000000001</v>
       </c>
       <c r="F47">
-        <v>105.75</v>
+        <v>108.1</v>
       </c>
       <c r="G47">
         <v>7.77</v>
@@ -5141,28 +5141,28 @@
         <v>23.5</v>
       </c>
       <c r="M47">
-        <v>6.482475</v>
+        <v>6.626530000000001</v>
       </c>
       <c r="N47">
-        <v>17.017525</v>
+        <v>16.87347</v>
       </c>
       <c r="O47">
-        <v>2.55262875</v>
+        <v>2.531020499999999</v>
       </c>
       <c r="P47">
-        <v>14.46489625</v>
+        <v>14.3424495</v>
       </c>
       <c r="Q47">
-        <v>21.66489625</v>
+        <v>21.5424495</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1362552119930534</v>
+        <v>0.1377821096237573</v>
       </c>
       <c r="T47">
-        <v>1.656718974211106</v>
+        <v>1.684684640541747</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.62515860068878</v>
+        <v>3.546350805021632</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09837063919682897</v>
+        <v>0.09947226179747856</v>
       </c>
       <c r="C48">
-        <v>133.3233579875738</v>
+        <v>126.177625308224</v>
       </c>
       <c r="D48">
-        <v>233.6533579875738</v>
+        <v>228.857625308224</v>
       </c>
       <c r="E48">
-        <v>40.50000000000001</v>
+        <v>42.85000000000001</v>
       </c>
       <c r="F48">
-        <v>108.1</v>
+        <v>110.45</v>
       </c>
       <c r="G48">
         <v>7.77</v>
@@ -5223,45 +5223,45 @@
         <v>23.5</v>
       </c>
       <c r="M48">
-        <v>6.626530000000001</v>
+        <v>7.079845000000001</v>
       </c>
       <c r="N48">
-        <v>16.87347</v>
+        <v>16.420155</v>
       </c>
       <c r="O48">
-        <v>2.531020499999999</v>
+        <v>2.46302325</v>
       </c>
       <c r="P48">
-        <v>14.3424495</v>
+        <v>13.95713175</v>
       </c>
       <c r="Q48">
-        <v>21.5424495</v>
+        <v>21.15713175</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1377821096237573</v>
+        <v>0.1393666260329784</v>
       </c>
       <c r="T48">
-        <v>1.684684640541747</v>
+        <v>1.713705615035809</v>
       </c>
       <c r="U48">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V48">
         <v>0.15</v>
       </c>
       <c r="W48">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>3.546350805021632</v>
+        <v>3.31928170743851</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09947226179747856</v>
+        <v>0.09947908439812811</v>
       </c>
       <c r="C49">
-        <v>126.177625308224</v>
+        <v>123.7985375508491</v>
       </c>
       <c r="D49">
-        <v>228.857625308224</v>
+        <v>228.8285375508491</v>
       </c>
       <c r="E49">
-        <v>42.85000000000001</v>
+        <v>45.20000000000002</v>
       </c>
       <c r="F49">
-        <v>110.45</v>
+        <v>112.8</v>
       </c>
       <c r="G49">
         <v>7.77</v>
@@ -5305,28 +5305,28 @@
         <v>23.5</v>
       </c>
       <c r="M49">
-        <v>7.079845000000001</v>
+        <v>7.230480000000001</v>
       </c>
       <c r="N49">
-        <v>16.420155</v>
+        <v>16.26952</v>
       </c>
       <c r="O49">
-        <v>2.46302325</v>
+        <v>2.440428</v>
       </c>
       <c r="P49">
-        <v>13.95713175</v>
+        <v>13.829092</v>
       </c>
       <c r="Q49">
-        <v>21.15713175</v>
+        <v>21.029092</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1393666260329784</v>
+        <v>0.1410120853810156</v>
       </c>
       <c r="T49">
-        <v>1.713705615035809</v>
+        <v>1.743842780856565</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.31928170743851</v>
+        <v>3.250130005200208</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09947908439812811</v>
+        <v>0.0994859069987777</v>
       </c>
       <c r="C50">
-        <v>123.7985375508491</v>
+        <v>121.4194571866303</v>
       </c>
       <c r="D50">
-        <v>228.8285375508491</v>
+        <v>228.7994571866303</v>
       </c>
       <c r="E50">
-        <v>45.2</v>
+        <v>47.55</v>
       </c>
       <c r="F50">
-        <v>112.8</v>
+        <v>115.15</v>
       </c>
       <c r="G50">
         <v>7.77</v>
@@ -5387,28 +5387,28 @@
         <v>23.5</v>
       </c>
       <c r="M50">
-        <v>7.23048</v>
+        <v>7.381115</v>
       </c>
       <c r="N50">
-        <v>16.26952</v>
+        <v>16.118885</v>
       </c>
       <c r="O50">
-        <v>2.440428</v>
+        <v>2.41783275</v>
       </c>
       <c r="P50">
-        <v>13.829092</v>
+        <v>13.70105225</v>
       </c>
       <c r="Q50">
-        <v>21.029092</v>
+        <v>20.90105225</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1410120853810156</v>
+        <v>0.1427220725466229</v>
       </c>
       <c r="T50">
-        <v>1.743842780856565</v>
+        <v>1.775161796317351</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.250130005200208</v>
+        <v>3.183800821420612</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0994859069987777</v>
+        <v>0.09949272959942727</v>
       </c>
       <c r="C51">
-        <v>121.4194571866303</v>
+        <v>119.0403842127497</v>
       </c>
       <c r="D51">
-        <v>228.7994571866303</v>
+        <v>228.7703842127497</v>
       </c>
       <c r="E51">
-        <v>47.55</v>
+        <v>49.90000000000001</v>
       </c>
       <c r="F51">
-        <v>115.15</v>
+        <v>117.5</v>
       </c>
       <c r="G51">
         <v>7.77</v>
@@ -5469,28 +5469,28 @@
         <v>23.5</v>
       </c>
       <c r="M51">
-        <v>7.381115</v>
+        <v>7.531750000000001</v>
       </c>
       <c r="N51">
-        <v>16.118885</v>
+        <v>15.96825</v>
       </c>
       <c r="O51">
-        <v>2.41783275</v>
+        <v>2.3952375</v>
       </c>
       <c r="P51">
-        <v>13.70105225</v>
+        <v>13.5730125</v>
       </c>
       <c r="Q51">
-        <v>20.90105225</v>
+        <v>20.7730125</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1427220725466229</v>
+        <v>0.1445004591988545</v>
       </c>
       <c r="T51">
-        <v>1.775161796317351</v>
+        <v>1.807733572396569</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.183800821420612</v>
+        <v>3.120124804992199</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09949272959942727</v>
+        <v>0.09949955220007685</v>
       </c>
       <c r="C52">
-        <v>119.0403842127497</v>
+        <v>116.6613186263903</v>
       </c>
       <c r="D52">
-        <v>228.7703842127497</v>
+        <v>228.7413186263903</v>
       </c>
       <c r="E52">
-        <v>49.90000000000001</v>
+        <v>52.25000000000001</v>
       </c>
       <c r="F52">
-        <v>117.5</v>
+        <v>119.85</v>
       </c>
       <c r="G52">
         <v>7.77</v>
@@ -5551,28 +5551,28 @@
         <v>23.5</v>
       </c>
       <c r="M52">
-        <v>7.531750000000001</v>
+        <v>7.682385000000001</v>
       </c>
       <c r="N52">
-        <v>15.96825</v>
+        <v>15.817615</v>
       </c>
       <c r="O52">
-        <v>2.3952375</v>
+        <v>2.37264225</v>
       </c>
       <c r="P52">
-        <v>13.5730125</v>
+        <v>13.44497275</v>
       </c>
       <c r="Q52">
-        <v>20.7730125</v>
+        <v>20.64497275</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1445004591988545</v>
+        <v>0.1463514330613813</v>
       </c>
       <c r="T52">
-        <v>1.807733572396569</v>
+        <v>1.841634808723918</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.120124804992199</v>
+        <v>3.058945887247254</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09949955220007685</v>
+        <v>0.09950637480072644</v>
       </c>
       <c r="C53">
-        <v>116.6613186263903</v>
+        <v>114.2822604247366</v>
       </c>
       <c r="D53">
-        <v>228.7413186263903</v>
+        <v>228.7122604247366</v>
       </c>
       <c r="E53">
-        <v>52.25000000000001</v>
+        <v>54.60000000000001</v>
       </c>
       <c r="F53">
-        <v>119.85</v>
+        <v>122.2</v>
       </c>
       <c r="G53">
         <v>7.77</v>
@@ -5633,28 +5633,28 @@
         <v>23.5</v>
       </c>
       <c r="M53">
-        <v>7.682385000000001</v>
+        <v>7.83302</v>
       </c>
       <c r="N53">
-        <v>15.817615</v>
+        <v>15.66698</v>
       </c>
       <c r="O53">
-        <v>2.37264225</v>
+        <v>2.350047</v>
       </c>
       <c r="P53">
-        <v>13.44497275</v>
+        <v>13.316933</v>
       </c>
       <c r="Q53">
-        <v>20.64497275</v>
+        <v>20.516933</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1463514330613813</v>
+        <v>0.1482795308348467</v>
       </c>
       <c r="T53">
-        <v>1.841634808723918</v>
+        <v>1.876948596564906</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.058945887247254</v>
+        <v>3.000120004800192</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09950637480072644</v>
+        <v>0.103027097401376</v>
       </c>
       <c r="C54">
-        <v>114.2822604247366</v>
+        <v>97.86143627170767</v>
       </c>
       <c r="D54">
-        <v>228.7122604247366</v>
+        <v>214.6414362717077</v>
       </c>
       <c r="E54">
-        <v>54.60000000000001</v>
+        <v>56.95000000000002</v>
       </c>
       <c r="F54">
-        <v>122.2</v>
+        <v>124.55</v>
       </c>
       <c r="G54">
         <v>7.77</v>
@@ -5715,45 +5715,45 @@
         <v>23.5</v>
       </c>
       <c r="M54">
-        <v>7.83302</v>
+        <v>8.955145000000002</v>
       </c>
       <c r="N54">
-        <v>15.66698</v>
+        <v>14.544855</v>
       </c>
       <c r="O54">
-        <v>2.350047</v>
+        <v>2.181728249999999</v>
       </c>
       <c r="P54">
-        <v>13.316933</v>
+        <v>12.36312675</v>
       </c>
       <c r="Q54">
-        <v>20.516933</v>
+        <v>19.56312675</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1482795308348467</v>
+        <v>0.1502896753220766</v>
       </c>
       <c r="T54">
-        <v>1.876948596564906</v>
+        <v>1.913765098782106</v>
       </c>
       <c r="U54">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V54">
         <v>0.15</v>
       </c>
       <c r="W54">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>3.000120004800192</v>
+        <v>2.624189781404991</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.103027097401376</v>
+        <v>0.1031002200020256</v>
       </c>
       <c r="C55">
-        <v>97.86143627170767</v>
+        <v>95.23752563005928</v>
       </c>
       <c r="D55">
-        <v>214.6414362717077</v>
+        <v>214.3675256300593</v>
       </c>
       <c r="E55">
-        <v>56.95000000000002</v>
+        <v>59.30000000000001</v>
       </c>
       <c r="F55">
-        <v>124.55</v>
+        <v>126.9</v>
       </c>
       <c r="G55">
         <v>7.77</v>
@@ -5797,28 +5797,28 @@
         <v>23.5</v>
       </c>
       <c r="M55">
-        <v>8.955145000000002</v>
+        <v>9.124110000000002</v>
       </c>
       <c r="N55">
-        <v>14.544855</v>
+        <v>14.37589</v>
       </c>
       <c r="O55">
-        <v>2.181728249999999</v>
+        <v>2.1563835</v>
       </c>
       <c r="P55">
-        <v>12.36312675</v>
+        <v>12.2195065</v>
       </c>
       <c r="Q55">
-        <v>19.56312675</v>
+        <v>19.4195065</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1502896753220766</v>
+        <v>0.1523872173957078</v>
       </c>
       <c r="T55">
-        <v>1.913765098782106</v>
+        <v>1.952182318487012</v>
       </c>
       <c r="U55">
         <v>0.07190000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.624189781404991</v>
+        <v>2.575593674341936</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1031002200020256</v>
+        <v>0.1031733426026752</v>
       </c>
       <c r="C56">
-        <v>95.23752563005928</v>
+        <v>92.61431318926708</v>
       </c>
       <c r="D56">
-        <v>214.3675256300593</v>
+        <v>214.0943131892671</v>
       </c>
       <c r="E56">
-        <v>59.30000000000001</v>
+        <v>61.65000000000001</v>
       </c>
       <c r="F56">
-        <v>126.9</v>
+        <v>129.25</v>
       </c>
       <c r="G56">
         <v>7.77</v>
@@ -5879,28 +5879,28 @@
         <v>23.5</v>
       </c>
       <c r="M56">
-        <v>9.124110000000002</v>
+        <v>9.293075</v>
       </c>
       <c r="N56">
-        <v>14.37589</v>
+        <v>14.206925</v>
       </c>
       <c r="O56">
-        <v>2.1563835</v>
+        <v>2.13103875</v>
       </c>
       <c r="P56">
-        <v>12.2195065</v>
+        <v>12.07588625</v>
       </c>
       <c r="Q56">
-        <v>19.4195065</v>
+        <v>19.27588625</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1523872173957078</v>
+        <v>0.1545779835615004</v>
       </c>
       <c r="T56">
-        <v>1.952182318487012</v>
+        <v>1.992306970178801</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.575593674341936</v>
+        <v>2.52876469844481</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1031733426026752</v>
+        <v>0.1051028652033247</v>
       </c>
       <c r="C57">
-        <v>92.61431318926708</v>
+        <v>83.29837967909191</v>
       </c>
       <c r="D57">
-        <v>214.0943131892671</v>
+        <v>207.1283796790919</v>
       </c>
       <c r="E57">
-        <v>61.65000000000001</v>
+        <v>64.00000000000003</v>
       </c>
       <c r="F57">
-        <v>129.25</v>
+        <v>131.6</v>
       </c>
       <c r="G57">
         <v>7.77</v>
@@ -5961,45 +5961,45 @@
         <v>23.5</v>
       </c>
       <c r="M57">
-        <v>9.293075</v>
+        <v>9.975280000000003</v>
       </c>
       <c r="N57">
-        <v>14.206925</v>
+        <v>13.52472</v>
       </c>
       <c r="O57">
-        <v>2.13103875</v>
+        <v>2.028708</v>
       </c>
       <c r="P57">
-        <v>12.07588625</v>
+        <v>11.496012</v>
       </c>
       <c r="Q57">
-        <v>19.27588625</v>
+        <v>18.696012</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1545779835615004</v>
+        <v>0.1568683300075562</v>
       </c>
       <c r="T57">
-        <v>1.992306970178801</v>
+        <v>2.034255469674763</v>
       </c>
       <c r="U57">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V57">
         <v>0.15</v>
       </c>
       <c r="W57">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.52876469844481</v>
+        <v>2.355823595929136</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1051028652033247</v>
+        <v>0.1052091378039743</v>
       </c>
       <c r="C58">
-        <v>83.29837967909191</v>
+        <v>80.57786308197416</v>
       </c>
       <c r="D58">
-        <v>207.1283796790919</v>
+        <v>206.7578630819742</v>
       </c>
       <c r="E58">
-        <v>64.00000000000003</v>
+        <v>66.35000000000002</v>
       </c>
       <c r="F58">
-        <v>131.6</v>
+        <v>133.95</v>
       </c>
       <c r="G58">
         <v>7.77</v>
@@ -6043,28 +6043,28 @@
         <v>23.5</v>
       </c>
       <c r="M58">
-        <v>9.975280000000003</v>
+        <v>10.15341</v>
       </c>
       <c r="N58">
-        <v>13.52472</v>
+        <v>13.34659</v>
       </c>
       <c r="O58">
-        <v>2.028708</v>
+        <v>2.0019885</v>
       </c>
       <c r="P58">
-        <v>11.496012</v>
+        <v>11.3446015</v>
       </c>
       <c r="Q58">
-        <v>18.696012</v>
+        <v>18.5446015</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1568683300075562</v>
+        <v>0.1592652041952891</v>
       </c>
       <c r="T58">
-        <v>2.034255469674763</v>
+        <v>2.078155062170537</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.355823595929136</v>
+        <v>2.314493357404063</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1052091378039743</v>
+        <v>0.1053154104046239</v>
       </c>
       <c r="C59">
-        <v>80.57786308197416</v>
+        <v>77.85866969718379</v>
       </c>
       <c r="D59">
-        <v>206.7578630819742</v>
+        <v>206.3886696971838</v>
       </c>
       <c r="E59">
-        <v>66.35000000000002</v>
+        <v>68.70000000000002</v>
       </c>
       <c r="F59">
-        <v>133.95</v>
+        <v>136.3</v>
       </c>
       <c r="G59">
         <v>7.77</v>
@@ -6125,28 +6125,28 @@
         <v>23.5</v>
       </c>
       <c r="M59">
-        <v>10.15341</v>
+        <v>10.33154</v>
       </c>
       <c r="N59">
-        <v>13.34659</v>
+        <v>13.16846</v>
       </c>
       <c r="O59">
-        <v>2.0019885</v>
+        <v>1.975268999999999</v>
       </c>
       <c r="P59">
-        <v>11.3446015</v>
+        <v>11.193191</v>
       </c>
       <c r="Q59">
-        <v>18.5446015</v>
+        <v>18.393191</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1592652041952891</v>
+        <v>0.1617762152491045</v>
       </c>
       <c r="T59">
-        <v>2.078155062170537</v>
+        <v>2.124145111451824</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.314493357404063</v>
+        <v>2.274588299517787</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1053154104046239</v>
+        <v>0.1054216830052735</v>
       </c>
       <c r="C60">
-        <v>77.85866969718381</v>
+        <v>75.14079244904596</v>
       </c>
       <c r="D60">
-        <v>206.3886696971838</v>
+        <v>206.020792449046</v>
       </c>
       <c r="E60">
-        <v>68.69999999999999</v>
+        <v>71.05000000000001</v>
       </c>
       <c r="F60">
-        <v>136.3</v>
+        <v>138.65</v>
       </c>
       <c r="G60">
         <v>7.77</v>
@@ -6207,28 +6207,28 @@
         <v>23.5</v>
       </c>
       <c r="M60">
-        <v>10.33154</v>
+        <v>10.50967</v>
       </c>
       <c r="N60">
-        <v>13.16846</v>
+        <v>12.99033</v>
       </c>
       <c r="O60">
-        <v>1.975269</v>
+        <v>1.9485495</v>
       </c>
       <c r="P60">
-        <v>11.193191</v>
+        <v>11.0417805</v>
       </c>
       <c r="Q60">
-        <v>18.393191</v>
+        <v>18.2417805</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1617762152491045</v>
+        <v>0.1644097146470084</v>
       </c>
       <c r="T60">
-        <v>2.124145111451824</v>
+        <v>2.172378577771222</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.274588299517787</v>
+        <v>2.236035955458163</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1054216830052735</v>
+        <v>0.105527955605923</v>
       </c>
       <c r="C61">
-        <v>75.14079244904596</v>
+        <v>72.42422431224412</v>
       </c>
       <c r="D61">
-        <v>206.020792449046</v>
+        <v>205.6542243122441</v>
       </c>
       <c r="E61">
-        <v>71.05000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F61">
-        <v>138.65</v>
+        <v>141</v>
       </c>
       <c r="G61">
         <v>7.77</v>
@@ -6289,28 +6289,28 @@
         <v>23.5</v>
       </c>
       <c r="M61">
-        <v>10.50967</v>
+        <v>10.6878</v>
       </c>
       <c r="N61">
-        <v>12.99033</v>
+        <v>12.8122</v>
       </c>
       <c r="O61">
-        <v>1.9485495</v>
+        <v>1.92183</v>
       </c>
       <c r="P61">
-        <v>11.0417805</v>
+        <v>10.89037</v>
       </c>
       <c r="Q61">
-        <v>18.2417805</v>
+        <v>18.09037</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1644097146470084</v>
+        <v>0.1671748890148076</v>
       </c>
       <c r="T61">
-        <v>2.172378577771222</v>
+        <v>2.223023717406591</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.236035955458163</v>
+        <v>2.198768689533861</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.105527955605923</v>
+        <v>0.1056342282065726</v>
       </c>
       <c r="C62">
-        <v>72.42422431224412</v>
+        <v>69.70895831137284</v>
       </c>
       <c r="D62">
-        <v>205.6542243122441</v>
+        <v>205.2889583113728</v>
       </c>
       <c r="E62">
-        <v>73.40000000000001</v>
+        <v>75.75</v>
       </c>
       <c r="F62">
-        <v>141</v>
+        <v>143.35</v>
       </c>
       <c r="G62">
         <v>7.77</v>
@@ -6371,28 +6371,28 @@
         <v>23.5</v>
       </c>
       <c r="M62">
-        <v>10.6878</v>
+        <v>10.86593</v>
       </c>
       <c r="N62">
-        <v>12.8122</v>
+        <v>12.63407</v>
       </c>
       <c r="O62">
-        <v>1.92183</v>
+        <v>1.8951105</v>
       </c>
       <c r="P62">
-        <v>10.89037</v>
+        <v>10.7389595</v>
       </c>
       <c r="Q62">
-        <v>18.09037</v>
+        <v>17.9389595</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1671748890148076</v>
+        <v>0.1700818671963401</v>
       </c>
       <c r="T62">
-        <v>2.223023717406591</v>
+        <v>2.276266043689927</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.198768689533861</v>
+        <v>2.162723301180847</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1056342282065726</v>
+        <v>0.1057405008072222</v>
       </c>
       <c r="C63">
-        <v>69.70895831137284</v>
+        <v>66.99498752049547</v>
       </c>
       <c r="D63">
-        <v>205.2889583113728</v>
+        <v>204.9249875204954</v>
       </c>
       <c r="E63">
-        <v>75.75</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="F63">
-        <v>143.35</v>
+        <v>145.7</v>
       </c>
       <c r="G63">
         <v>7.77</v>
@@ -6453,28 +6453,28 @@
         <v>23.5</v>
       </c>
       <c r="M63">
-        <v>10.86593</v>
+        <v>11.04406</v>
       </c>
       <c r="N63">
-        <v>12.63407</v>
+        <v>12.45594</v>
       </c>
       <c r="O63">
-        <v>1.8951105</v>
+        <v>1.868391</v>
       </c>
       <c r="P63">
-        <v>10.7389595</v>
+        <v>10.587549</v>
       </c>
       <c r="Q63">
-        <v>17.9389595</v>
+        <v>17.787549</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1700818671963401</v>
+        <v>0.1731418442295321</v>
       </c>
       <c r="T63">
-        <v>2.276266043689927</v>
+        <v>2.332310597672387</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.162723301180847</v>
+        <v>2.127840667290833</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1057405008072222</v>
+        <v>0.1058467734078718</v>
       </c>
       <c r="C64">
-        <v>66.99498752049547</v>
+        <v>64.28230506270609</v>
       </c>
       <c r="D64">
-        <v>204.9249875204954</v>
+        <v>204.5623050627061</v>
       </c>
       <c r="E64">
-        <v>78.09999999999999</v>
+        <v>80.45000000000002</v>
       </c>
       <c r="F64">
-        <v>145.7</v>
+        <v>148.05</v>
       </c>
       <c r="G64">
         <v>7.77</v>
@@ -6535,28 +6535,28 @@
         <v>23.5</v>
       </c>
       <c r="M64">
-        <v>11.04406</v>
+        <v>11.22219</v>
       </c>
       <c r="N64">
-        <v>12.45594</v>
+        <v>12.27781</v>
       </c>
       <c r="O64">
-        <v>1.868391</v>
+        <v>1.8416715</v>
       </c>
       <c r="P64">
-        <v>10.587549</v>
+        <v>10.4361385</v>
       </c>
       <c r="Q64">
-        <v>17.787549</v>
+        <v>17.6361385</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1731418442295321</v>
+        <v>0.1763672254266805</v>
       </c>
       <c r="T64">
-        <v>2.332310597672387</v>
+        <v>2.391384587005249</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.127840667290833</v>
+        <v>2.094065418603677</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1058467734078718</v>
+        <v>0.1059530460085213</v>
       </c>
       <c r="C65">
-        <v>64.28230506270609</v>
+        <v>61.57090410969693</v>
       </c>
       <c r="D65">
-        <v>204.5623050627061</v>
+        <v>204.2009041096969</v>
       </c>
       <c r="E65">
-        <v>80.45000000000002</v>
+        <v>82.80000000000001</v>
       </c>
       <c r="F65">
-        <v>148.05</v>
+        <v>150.4</v>
       </c>
       <c r="G65">
         <v>7.77</v>
@@ -6617,28 +6617,28 @@
         <v>23.5</v>
       </c>
       <c r="M65">
-        <v>11.22219</v>
+        <v>11.40032</v>
       </c>
       <c r="N65">
-        <v>12.27781</v>
+        <v>12.09968</v>
       </c>
       <c r="O65">
-        <v>1.8416715</v>
+        <v>1.814952</v>
       </c>
       <c r="P65">
-        <v>10.4361385</v>
+        <v>10.284728</v>
       </c>
       <c r="Q65">
-        <v>17.6361385</v>
+        <v>17.484728</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1763672254266805</v>
+        <v>0.1797717944681149</v>
       </c>
       <c r="T65">
-        <v>2.391384587005249</v>
+        <v>2.453740464634381</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.094065418603677</v>
+        <v>2.061345646437995</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1059530460085213</v>
+        <v>0.1060593186091709</v>
       </c>
       <c r="C66">
-        <v>61.57090410969693</v>
+        <v>58.86077788132914</v>
       </c>
       <c r="D66">
-        <v>204.2009041096969</v>
+        <v>203.8407778813291</v>
       </c>
       <c r="E66">
-        <v>82.80000000000001</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="F66">
-        <v>150.4</v>
+        <v>152.75</v>
       </c>
       <c r="G66">
         <v>7.77</v>
@@ -6699,28 +6699,28 @@
         <v>23.5</v>
       </c>
       <c r="M66">
-        <v>11.40032</v>
+        <v>11.57845</v>
       </c>
       <c r="N66">
-        <v>12.09968</v>
+        <v>11.92155</v>
       </c>
       <c r="O66">
-        <v>1.814952</v>
+        <v>1.7882325</v>
       </c>
       <c r="P66">
-        <v>10.284728</v>
+        <v>10.1333175</v>
       </c>
       <c r="Q66">
-        <v>17.484728</v>
+        <v>17.3333175</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1797717944681149</v>
+        <v>0.183370910311917</v>
       </c>
       <c r="T66">
-        <v>2.453740464634381</v>
+        <v>2.519659535270893</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.061345646437995</v>
+        <v>2.029632636492795</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1060593186091709</v>
+        <v>0.1141317912098205</v>
       </c>
       <c r="C67">
-        <v>58.86077788132914</v>
+        <v>32.42975987772618</v>
       </c>
       <c r="D67">
-        <v>203.8407778813291</v>
+        <v>179.7597598777262</v>
       </c>
       <c r="E67">
-        <v>85.15000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="F67">
-        <v>152.75</v>
+        <v>155.1</v>
       </c>
       <c r="G67">
         <v>7.77</v>
@@ -6781,45 +6781,45 @@
         <v>23.5</v>
       </c>
       <c r="M67">
-        <v>11.57845</v>
+        <v>13.959</v>
       </c>
       <c r="N67">
-        <v>11.92155</v>
+        <v>9.541</v>
       </c>
       <c r="O67">
-        <v>1.7882325</v>
+        <v>1.43115</v>
       </c>
       <c r="P67">
-        <v>10.1333175</v>
+        <v>8.10985</v>
       </c>
       <c r="Q67">
-        <v>17.3333175</v>
+        <v>15.30985</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.183370910311917</v>
+        <v>0.1871817388524133</v>
       </c>
       <c r="T67">
-        <v>2.519659535270893</v>
+        <v>2.589456198297788</v>
       </c>
       <c r="U67">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V67">
         <v>0.15</v>
       </c>
       <c r="W67">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.029632636492795</v>
+        <v>1.683501683501683</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1141317912098205</v>
+        <v>0.1143587638104701</v>
       </c>
       <c r="C68">
-        <v>32.42975987772618</v>
+        <v>29.48464208499024</v>
       </c>
       <c r="D68">
-        <v>179.7597598777262</v>
+        <v>179.1646420849902</v>
       </c>
       <c r="E68">
-        <v>87.5</v>
+        <v>89.85000000000002</v>
       </c>
       <c r="F68">
-        <v>155.1</v>
+        <v>157.45</v>
       </c>
       <c r="G68">
         <v>7.77</v>
@@ -6863,28 +6863,28 @@
         <v>23.5</v>
       </c>
       <c r="M68">
-        <v>13.959</v>
+        <v>14.1705</v>
       </c>
       <c r="N68">
-        <v>9.541</v>
+        <v>9.329499999999999</v>
       </c>
       <c r="O68">
-        <v>1.43115</v>
+        <v>1.399425</v>
       </c>
       <c r="P68">
-        <v>8.10985</v>
+        <v>7.930075</v>
       </c>
       <c r="Q68">
-        <v>15.30985</v>
+        <v>15.130075</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1871817388524133</v>
+        <v>0.1912235266983942</v>
       </c>
       <c r="T68">
-        <v>2.589456198297788</v>
+        <v>2.663482962114191</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.683501683501683</v>
+        <v>1.658374792703151</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1143587638104701</v>
+        <v>0.1145857364111197</v>
       </c>
       <c r="C69">
-        <v>29.48464208499024</v>
+        <v>26.54345171791425</v>
       </c>
       <c r="D69">
-        <v>179.1646420849902</v>
+        <v>178.5734517179143</v>
       </c>
       <c r="E69">
-        <v>89.85000000000002</v>
+        <v>92.20000000000002</v>
       </c>
       <c r="F69">
-        <v>157.45</v>
+        <v>159.8</v>
       </c>
       <c r="G69">
         <v>7.77</v>
@@ -6945,28 +6945,28 @@
         <v>23.5</v>
       </c>
       <c r="M69">
-        <v>14.1705</v>
+        <v>14.382</v>
       </c>
       <c r="N69">
-        <v>9.329499999999999</v>
+        <v>9.118</v>
       </c>
       <c r="O69">
-        <v>1.399425</v>
+        <v>1.3677</v>
       </c>
       <c r="P69">
-        <v>7.930075</v>
+        <v>7.7503</v>
       </c>
       <c r="Q69">
-        <v>15.130075</v>
+        <v>14.9503</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1912235266983942</v>
+        <v>0.195517926284749</v>
       </c>
       <c r="T69">
-        <v>2.663482962114191</v>
+        <v>2.74213639866912</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.658374792703151</v>
+        <v>1.633986928104575</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1145857364111197</v>
+        <v>0.1148127090117693</v>
       </c>
       <c r="C70">
-        <v>26.54345171791425</v>
+        <v>23.60615002633054</v>
       </c>
       <c r="D70">
-        <v>178.5734517179143</v>
+        <v>177.9861500263305</v>
       </c>
       <c r="E70">
-        <v>92.20000000000002</v>
+        <v>94.55000000000001</v>
       </c>
       <c r="F70">
-        <v>159.8</v>
+        <v>162.15</v>
       </c>
       <c r="G70">
         <v>7.77</v>
@@ -7027,28 +7027,28 @@
         <v>23.5</v>
       </c>
       <c r="M70">
-        <v>14.382</v>
+        <v>14.5935</v>
       </c>
       <c r="N70">
-        <v>9.118</v>
+        <v>8.906499999999999</v>
       </c>
       <c r="O70">
-        <v>1.3677</v>
+        <v>1.335975</v>
       </c>
       <c r="P70">
-        <v>7.7503</v>
+        <v>7.570525</v>
       </c>
       <c r="Q70">
-        <v>14.9503</v>
+        <v>14.770525</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.195517926284749</v>
+        <v>0.2000893839089331</v>
       </c>
       <c r="T70">
-        <v>2.74213639866912</v>
+        <v>2.825864250485657</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.633986928104575</v>
+        <v>1.610305958132045</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1148127090117693</v>
+        <v>0.1150396816124188</v>
       </c>
       <c r="C71">
-        <v>23.60615002633054</v>
+        <v>20.6726987681746</v>
       </c>
       <c r="D71">
-        <v>177.9861500263305</v>
+        <v>177.4026987681746</v>
       </c>
       <c r="E71">
-        <v>94.55000000000001</v>
+        <v>96.90000000000003</v>
       </c>
       <c r="F71">
-        <v>162.15</v>
+        <v>164.5</v>
       </c>
       <c r="G71">
         <v>7.77</v>
@@ -7109,28 +7109,28 @@
         <v>23.5</v>
       </c>
       <c r="M71">
-        <v>14.5935</v>
+        <v>14.805</v>
       </c>
       <c r="N71">
-        <v>8.906499999999999</v>
+        <v>8.694999999999999</v>
       </c>
       <c r="O71">
-        <v>1.335975</v>
+        <v>1.30425</v>
       </c>
       <c r="P71">
-        <v>7.570525</v>
+        <v>7.390749999999999</v>
       </c>
       <c r="Q71">
-        <v>14.770525</v>
+        <v>14.59075</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2000893839089331</v>
+        <v>0.2049656053747294</v>
       </c>
       <c r="T71">
-        <v>2.825864250485657</v>
+        <v>2.915173959089963</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.610305958132045</v>
+        <v>1.587301587301587</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1150396816124188</v>
+        <v>0.1152666542130684</v>
       </c>
       <c r="C72">
-        <v>20.6726987681746</v>
+        <v>17.74306020118442</v>
       </c>
       <c r="D72">
-        <v>177.4026987681746</v>
+        <v>176.8230602011844</v>
       </c>
       <c r="E72">
-        <v>96.90000000000003</v>
+        <v>99.25000000000003</v>
       </c>
       <c r="F72">
-        <v>164.5</v>
+        <v>166.85</v>
       </c>
       <c r="G72">
         <v>7.77</v>
@@ -7191,28 +7191,28 @@
         <v>23.5</v>
       </c>
       <c r="M72">
-        <v>14.805</v>
+        <v>15.0165</v>
       </c>
       <c r="N72">
-        <v>8.694999999999999</v>
+        <v>8.483499999999999</v>
       </c>
       <c r="O72">
-        <v>1.30425</v>
+        <v>1.272525</v>
       </c>
       <c r="P72">
-        <v>7.390749999999999</v>
+        <v>7.210974999999999</v>
       </c>
       <c r="Q72">
-        <v>14.59075</v>
+        <v>14.410975</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2049656053747294</v>
+        <v>0.210178117976098</v>
       </c>
       <c r="T72">
-        <v>2.915173959089963</v>
+        <v>3.010642957942842</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.587301587301587</v>
+        <v>1.564945226917058</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1152666542130684</v>
+        <v>0.115493626813718</v>
       </c>
       <c r="C73">
-        <v>17.74306020118445</v>
+        <v>14.81719707476182</v>
       </c>
       <c r="D73">
-        <v>176.8230602011844</v>
+        <v>176.2471970747618</v>
       </c>
       <c r="E73">
-        <v>99.25</v>
+        <v>101.6</v>
       </c>
       <c r="F73">
-        <v>166.85</v>
+        <v>169.2</v>
       </c>
       <c r="G73">
         <v>7.77</v>
@@ -7273,28 +7273,28 @@
         <v>23.5</v>
       </c>
       <c r="M73">
-        <v>15.0165</v>
+        <v>15.228</v>
       </c>
       <c r="N73">
-        <v>8.483500000000001</v>
+        <v>8.272000000000002</v>
       </c>
       <c r="O73">
-        <v>1.272525</v>
+        <v>1.2408</v>
       </c>
       <c r="P73">
-        <v>7.210975000000001</v>
+        <v>7.031200000000002</v>
       </c>
       <c r="Q73">
-        <v>14.410975</v>
+        <v>14.2312</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2101781179760979</v>
+        <v>0.2157629529061356</v>
       </c>
       <c r="T73">
-        <v>3.010642957942841</v>
+        <v>3.112931170999496</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.564945226917058</v>
+        <v>1.54320987654321</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.115493626813718</v>
+        <v>0.1157205994143675</v>
       </c>
       <c r="C74">
-        <v>14.81719707476182</v>
+        <v>11.8950726219924</v>
       </c>
       <c r="D74">
-        <v>176.2471970747618</v>
+        <v>175.6750726219924</v>
       </c>
       <c r="E74">
-        <v>101.6</v>
+        <v>103.95</v>
       </c>
       <c r="F74">
-        <v>169.2</v>
+        <v>171.55</v>
       </c>
       <c r="G74">
         <v>7.77</v>
@@ -7355,28 +7355,28 @@
         <v>23.5</v>
       </c>
       <c r="M74">
-        <v>15.228</v>
+        <v>15.4395</v>
       </c>
       <c r="N74">
-        <v>8.272000000000002</v>
+        <v>8.060500000000003</v>
       </c>
       <c r="O74">
-        <v>1.2408</v>
+        <v>1.209075</v>
       </c>
       <c r="P74">
-        <v>7.031200000000002</v>
+        <v>6.851425000000003</v>
       </c>
       <c r="Q74">
-        <v>14.2312</v>
+        <v>14.051425</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2157629529061356</v>
+        <v>0.2217614793124724</v>
       </c>
       <c r="T74">
-        <v>3.112931170999496</v>
+        <v>3.222796288727016</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.54320987654321</v>
+        <v>1.522070015220701</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1157205994143675</v>
+        <v>0.1159475720150171</v>
       </c>
       <c r="C75">
-        <v>11.8950726219924</v>
+        <v>8.976650551820342</v>
       </c>
       <c r="D75">
-        <v>175.6750726219924</v>
+        <v>175.1066505518203</v>
       </c>
       <c r="E75">
-        <v>103.95</v>
+        <v>106.3</v>
       </c>
       <c r="F75">
-        <v>171.55</v>
+        <v>173.9</v>
       </c>
       <c r="G75">
         <v>7.77</v>
@@ -7437,28 +7437,28 @@
         <v>23.5</v>
       </c>
       <c r="M75">
-        <v>15.4395</v>
+        <v>15.651</v>
       </c>
       <c r="N75">
-        <v>8.060500000000003</v>
+        <v>7.849</v>
       </c>
       <c r="O75">
-        <v>1.209075</v>
+        <v>1.17735</v>
       </c>
       <c r="P75">
-        <v>6.851425000000003</v>
+        <v>6.671650000000001</v>
       </c>
       <c r="Q75">
-        <v>14.051425</v>
+        <v>13.87165</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2217614793124724</v>
+        <v>0.228221430826989</v>
       </c>
       <c r="T75">
-        <v>3.222796288727016</v>
+        <v>3.341112569356652</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.522070015220701</v>
+        <v>1.501501501501501</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1159475720150171</v>
+        <v>0.15445014184553</v>
       </c>
       <c r="C76">
-        <v>8.976650551820342</v>
+        <v>-55.42624626118143</v>
       </c>
       <c r="D76">
-        <v>175.1066505518203</v>
+        <v>113.0537537388186</v>
       </c>
       <c r="E76">
-        <v>106.3</v>
+        <v>108.65</v>
       </c>
       <c r="F76">
-        <v>173.9</v>
+        <v>176.25</v>
       </c>
       <c r="G76">
         <v>7.77</v>
@@ -7519,45 +7519,45 @@
         <v>23.5</v>
       </c>
       <c r="M76">
-        <v>15.651</v>
+        <v>25.8735</v>
       </c>
       <c r="N76">
-        <v>7.849</v>
+        <v>-2.373500000000003</v>
       </c>
       <c r="O76">
-        <v>1.17735</v>
+        <v>-0.3560250000000005</v>
       </c>
       <c r="P76">
-        <v>6.671650000000001</v>
+        <v>-2.017475000000003</v>
       </c>
       <c r="Q76">
-        <v>13.87165</v>
+        <v>5.182524999999996</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.228221430826989</v>
+        <v>0.2374005673821199</v>
       </c>
       <c r="T76">
-        <v>3.341112569356652</v>
+        <v>3.509231678943483</v>
       </c>
       <c r="U76">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.15</v>
+        <v>0.1362397820163488</v>
       </c>
       <c r="W76">
-        <v>0.0765</v>
+        <v>0.1268</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y76">
-        <v>1.501501501501501</v>
+        <v>0.908265213442325</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.15445014184553</v>
+        <v>0.15546014184553</v>
       </c>
       <c r="C77">
-        <v>-55.42624626118143</v>
+        <v>-58.8175023580142</v>
       </c>
       <c r="D77">
-        <v>113.0537537388186</v>
+        <v>112.0124976419858</v>
       </c>
       <c r="E77">
-        <v>108.65</v>
+        <v>111</v>
       </c>
       <c r="F77">
-        <v>176.25</v>
+        <v>178.6</v>
       </c>
       <c r="G77">
         <v>7.77</v>
@@ -7601,37 +7601,37 @@
         <v>23.5</v>
       </c>
       <c r="M77">
-        <v>25.8735</v>
+        <v>26.21848</v>
       </c>
       <c r="N77">
-        <v>-2.373500000000003</v>
+        <v>-2.718480000000003</v>
       </c>
       <c r="O77">
-        <v>-0.3560250000000005</v>
+        <v>-0.4077720000000005</v>
       </c>
       <c r="P77">
-        <v>-2.017475000000003</v>
+        <v>-2.310708000000003</v>
       </c>
       <c r="Q77">
-        <v>5.182524999999996</v>
+        <v>4.889291999999997</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2374005673821199</v>
+        <v>0.2453839243563749</v>
       </c>
       <c r="T77">
-        <v>3.509231678943483</v>
+        <v>3.655449665566128</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1362397820163488</v>
+        <v>0.1344471533056073</v>
       </c>
       <c r="W77">
-        <v>0.1268</v>
+        <v>0.1270631578947369</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.908265213442325</v>
+        <v>0.8963143553707155</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.15546014184553</v>
+        <v>0.15647014184553</v>
       </c>
       <c r="C78">
-        <v>-58.8175023580142</v>
+        <v>-62.18975299157999</v>
       </c>
       <c r="D78">
-        <v>112.0124976419858</v>
+        <v>110.99024700842</v>
       </c>
       <c r="E78">
-        <v>111</v>
+        <v>113.35</v>
       </c>
       <c r="F78">
-        <v>178.6</v>
+        <v>180.95</v>
       </c>
       <c r="G78">
         <v>7.77</v>
@@ -7683,37 +7683,37 @@
         <v>23.5</v>
       </c>
       <c r="M78">
-        <v>26.21848</v>
+        <v>26.56346000000001</v>
       </c>
       <c r="N78">
-        <v>-2.718480000000003</v>
+        <v>-3.063460000000006</v>
       </c>
       <c r="O78">
-        <v>-0.4077720000000005</v>
+        <v>-0.4595190000000009</v>
       </c>
       <c r="P78">
-        <v>-2.310708000000003</v>
+        <v>-2.603941000000005</v>
       </c>
       <c r="Q78">
-        <v>4.889291999999997</v>
+        <v>4.596058999999994</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2453839243563749</v>
+        <v>0.2540614862849129</v>
       </c>
       <c r="T78">
-        <v>3.655449665566128</v>
+        <v>3.814382259721177</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1344471533056073</v>
+        <v>0.1327010863795605</v>
       </c>
       <c r="W78">
-        <v>0.1270631578947369</v>
+        <v>0.1273194805194805</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8963143553707155</v>
+        <v>0.8846739091970698</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.15647014184553</v>
+        <v>0.15748014184553</v>
       </c>
       <c r="C79">
-        <v>-62.18975299157999</v>
+        <v>-65.54351380013587</v>
       </c>
       <c r="D79">
-        <v>110.99024700842</v>
+        <v>109.9864861998641</v>
       </c>
       <c r="E79">
-        <v>113.35</v>
+        <v>115.7</v>
       </c>
       <c r="F79">
-        <v>180.95</v>
+        <v>183.3</v>
       </c>
       <c r="G79">
         <v>7.77</v>
@@ -7765,37 +7765,37 @@
         <v>23.5</v>
       </c>
       <c r="M79">
-        <v>26.56346000000001</v>
+        <v>26.90844000000001</v>
       </c>
       <c r="N79">
-        <v>-3.063460000000006</v>
+        <v>-3.408440000000006</v>
       </c>
       <c r="O79">
-        <v>-0.4595190000000009</v>
+        <v>-0.5112660000000009</v>
       </c>
       <c r="P79">
-        <v>-2.603941000000005</v>
+        <v>-2.897174000000005</v>
       </c>
       <c r="Q79">
-        <v>4.596058999999994</v>
+        <v>4.302825999999994</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2540614862849129</v>
+        <v>0.2635279174796817</v>
       </c>
       <c r="T79">
-        <v>3.814382259721177</v>
+        <v>3.987763271526686</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1327010863795605</v>
+        <v>0.1309997904003353</v>
       </c>
       <c r="W79">
-        <v>0.1273194805194805</v>
+        <v>0.1275692307692308</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8846739091970698</v>
+        <v>0.8733319360022356</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.15748014184553</v>
+        <v>0.15849014184553</v>
       </c>
       <c r="C80">
-        <v>-65.54351380013587</v>
+        <v>-68.87928193604017</v>
       </c>
       <c r="D80">
-        <v>109.9864861998641</v>
+        <v>109.0007180639598</v>
       </c>
       <c r="E80">
-        <v>115.7</v>
+        <v>118.05</v>
       </c>
       <c r="F80">
-        <v>183.3</v>
+        <v>185.65</v>
       </c>
       <c r="G80">
         <v>7.77</v>
@@ -7847,37 +7847,37 @@
         <v>23.5</v>
       </c>
       <c r="M80">
-        <v>26.90844000000001</v>
+        <v>27.25342</v>
       </c>
       <c r="N80">
-        <v>-3.408440000000006</v>
+        <v>-3.753420000000002</v>
       </c>
       <c r="O80">
-        <v>-0.5112660000000009</v>
+        <v>-0.5630130000000003</v>
       </c>
       <c r="P80">
-        <v>-2.897174000000005</v>
+        <v>-3.190407000000002</v>
       </c>
       <c r="Q80">
-        <v>4.302825999999994</v>
+        <v>4.009592999999997</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2635279174796817</v>
+        <v>0.2738959135501428</v>
       </c>
       <c r="T80">
-        <v>3.987763271526686</v>
+        <v>4.177656760647004</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1309997904003353</v>
+        <v>0.1293415652053944</v>
       </c>
       <c r="W80">
-        <v>0.1275692307692308</v>
+        <v>0.1278126582278481</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8733319360022356</v>
+        <v>0.862277101369296</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.15849014184553</v>
+        <v>0.15950014184553</v>
       </c>
       <c r="C81">
-        <v>-68.87928193604017</v>
+        <v>-72.19753688680505</v>
       </c>
       <c r="D81">
-        <v>109.0007180639598</v>
+        <v>108.032463113195</v>
       </c>
       <c r="E81">
-        <v>118.05</v>
+        <v>120.4</v>
       </c>
       <c r="F81">
-        <v>185.65</v>
+        <v>188</v>
       </c>
       <c r="G81">
         <v>7.77</v>
@@ -7929,37 +7929,37 @@
         <v>23.5</v>
       </c>
       <c r="M81">
-        <v>27.25342</v>
+        <v>27.5984</v>
       </c>
       <c r="N81">
-        <v>-3.753420000000002</v>
+        <v>-4.098400000000002</v>
       </c>
       <c r="O81">
-        <v>-0.5630130000000003</v>
+        <v>-0.6147600000000002</v>
       </c>
       <c r="P81">
-        <v>-3.190407000000002</v>
+        <v>-3.483640000000001</v>
       </c>
       <c r="Q81">
-        <v>4.009592999999997</v>
+        <v>3.716359999999998</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2738959135501428</v>
+        <v>0.2853007092276499</v>
       </c>
       <c r="T81">
-        <v>4.177656760647004</v>
+        <v>4.386539598679355</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1293415652053944</v>
+        <v>0.127724795640327</v>
       </c>
       <c r="W81">
-        <v>0.1278126582278481</v>
+        <v>0.12805</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.862277101369296</v>
+        <v>0.8514986376021798</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.15950014184553</v>
+        <v>0.16051014184553</v>
       </c>
       <c r="C82">
-        <v>-72.19753688680505</v>
+        <v>-75.49874125277347</v>
       </c>
       <c r="D82">
-        <v>108.032463113195</v>
+        <v>107.0812587472266</v>
       </c>
       <c r="E82">
-        <v>120.4</v>
+        <v>122.75</v>
       </c>
       <c r="F82">
-        <v>188</v>
+        <v>190.35</v>
       </c>
       <c r="G82">
         <v>7.77</v>
@@ -8011,37 +8011,37 @@
         <v>23.5</v>
       </c>
       <c r="M82">
-        <v>27.5984</v>
+        <v>27.94338</v>
       </c>
       <c r="N82">
-        <v>-4.098400000000002</v>
+        <v>-4.443380000000005</v>
       </c>
       <c r="O82">
-        <v>-0.6147600000000002</v>
+        <v>-0.6665070000000007</v>
       </c>
       <c r="P82">
-        <v>-3.483640000000001</v>
+        <v>-3.776873000000004</v>
       </c>
       <c r="Q82">
-        <v>3.716359999999998</v>
+        <v>3.423126999999995</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2853007092276499</v>
+        <v>0.2979060097133157</v>
       </c>
       <c r="T82">
-        <v>4.386539598679355</v>
+        <v>4.617410103873005</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.127724795640327</v>
+        <v>0.126147946311434</v>
       </c>
       <c r="W82">
-        <v>0.12805</v>
+        <v>0.1282814814814815</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8514986376021798</v>
+        <v>0.8409863087428935</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.16051014184553</v>
+        <v>0.16152014184553</v>
       </c>
       <c r="C83">
-        <v>-75.49874125277347</v>
+        <v>-78.78334148407174</v>
       </c>
       <c r="D83">
-        <v>107.0812587472266</v>
+        <v>106.1466585159283</v>
       </c>
       <c r="E83">
-        <v>122.75</v>
+        <v>125.1</v>
       </c>
       <c r="F83">
-        <v>190.35</v>
+        <v>192.7</v>
       </c>
       <c r="G83">
         <v>7.77</v>
@@ -8093,37 +8093,37 @@
         <v>23.5</v>
       </c>
       <c r="M83">
-        <v>27.94338</v>
+        <v>28.28836</v>
       </c>
       <c r="N83">
-        <v>-4.443380000000005</v>
+        <v>-4.788360000000004</v>
       </c>
       <c r="O83">
-        <v>-0.6665070000000007</v>
+        <v>-0.7182540000000006</v>
       </c>
       <c r="P83">
-        <v>-3.776873000000004</v>
+        <v>-4.070106000000004</v>
       </c>
       <c r="Q83">
-        <v>3.423126999999995</v>
+        <v>3.129893999999996</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2979060097133157</v>
+        <v>0.3119118991418333</v>
       </c>
       <c r="T83">
-        <v>4.617410103873005</v>
+        <v>4.873932887421505</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.126147946311434</v>
+        <v>0.1246095567222702</v>
       </c>
       <c r="W83">
-        <v>0.1282814814814815</v>
+        <v>0.1285073170731708</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8409863087428935</v>
+        <v>0.8307303781484681</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.16152014184553</v>
+        <v>0.16253014184553</v>
       </c>
       <c r="C84">
-        <v>-78.78334148407174</v>
+        <v>-82.0517685793027</v>
       </c>
       <c r="D84">
-        <v>106.1466585159283</v>
+        <v>105.2282314206973</v>
       </c>
       <c r="E84">
-        <v>125.1</v>
+        <v>127.45</v>
       </c>
       <c r="F84">
-        <v>192.7</v>
+        <v>195.05</v>
       </c>
       <c r="G84">
         <v>7.77</v>
@@ -8175,37 +8175,37 @@
         <v>23.5</v>
       </c>
       <c r="M84">
-        <v>28.28836</v>
+        <v>28.63334</v>
       </c>
       <c r="N84">
-        <v>-4.788360000000004</v>
+        <v>-5.133340000000004</v>
       </c>
       <c r="O84">
-        <v>-0.7182540000000006</v>
+        <v>-0.7700010000000006</v>
       </c>
       <c r="P84">
-        <v>-4.070106000000004</v>
+        <v>-4.363339000000003</v>
       </c>
       <c r="Q84">
-        <v>3.129893999999996</v>
+        <v>2.836660999999996</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3119118991418333</v>
+        <v>0.3275655402678235</v>
       </c>
       <c r="T84">
-        <v>4.873932887421505</v>
+        <v>5.160634821975712</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1246095567222702</v>
+        <v>0.1231082367617609</v>
       </c>
       <c r="W84">
-        <v>0.1285073170731708</v>
+        <v>0.1287277108433735</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8307303781484681</v>
+        <v>0.8207215784117394</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.16253014184553</v>
+        <v>0.16354014184553</v>
       </c>
       <c r="C85">
-        <v>-82.0517685793027</v>
+        <v>-85.3044387482782</v>
       </c>
       <c r="D85">
-        <v>105.2282314206973</v>
+        <v>104.3255612517218</v>
       </c>
       <c r="E85">
-        <v>127.45</v>
+        <v>129.8</v>
       </c>
       <c r="F85">
-        <v>195.05</v>
+        <v>197.4</v>
       </c>
       <c r="G85">
         <v>7.77</v>
@@ -8257,37 +8257,37 @@
         <v>23.5</v>
       </c>
       <c r="M85">
-        <v>28.63334</v>
+        <v>28.97832</v>
       </c>
       <c r="N85">
-        <v>-5.133340000000004</v>
+        <v>-5.478320000000004</v>
       </c>
       <c r="O85">
-        <v>-0.7700010000000006</v>
+        <v>-0.8217480000000005</v>
       </c>
       <c r="P85">
-        <v>-4.363339000000003</v>
+        <v>-4.656572000000003</v>
       </c>
       <c r="Q85">
-        <v>2.836660999999996</v>
+        <v>2.543427999999996</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3275655402678235</v>
+        <v>0.3451758865345625</v>
       </c>
       <c r="T85">
-        <v>5.160634821975712</v>
+        <v>5.483174498349195</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1231082367617609</v>
+        <v>0.1216426625145971</v>
       </c>
       <c r="W85">
-        <v>0.1287277108433735</v>
+        <v>0.1289428571428572</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8207215784117394</v>
+        <v>0.8109510834306474</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.16354014184553</v>
+        <v>0.16455014184553</v>
       </c>
       <c r="C86">
-        <v>-85.3044387482782</v>
+        <v>-88.5417540409311</v>
       </c>
       <c r="D86">
-        <v>104.3255612517218</v>
+        <v>103.4382459590689</v>
       </c>
       <c r="E86">
-        <v>129.8</v>
+        <v>132.15</v>
       </c>
       <c r="F86">
-        <v>197.4</v>
+        <v>199.75</v>
       </c>
       <c r="G86">
         <v>7.77</v>
@@ -8339,37 +8339,37 @@
         <v>23.5</v>
       </c>
       <c r="M86">
-        <v>28.97832</v>
+        <v>29.3233</v>
       </c>
       <c r="N86">
-        <v>-5.478320000000004</v>
+        <v>-5.823300000000003</v>
       </c>
       <c r="O86">
-        <v>-0.8217480000000005</v>
+        <v>-0.8734950000000005</v>
       </c>
       <c r="P86">
-        <v>-4.656572000000003</v>
+        <v>-4.949805000000003</v>
       </c>
       <c r="Q86">
-        <v>2.543427999999996</v>
+        <v>2.250194999999996</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3451758865345623</v>
+        <v>0.3651342789701998</v>
       </c>
       <c r="T86">
-        <v>5.483174498349191</v>
+        <v>5.848719464905805</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.1216426625145971</v>
+        <v>0.1202115723673666</v>
       </c>
       <c r="W86">
-        <v>0.1289428571428572</v>
+        <v>0.1291529411764706</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8109510834306474</v>
+        <v>0.8014104824491104</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.16455014184553</v>
+        <v>0.2134661713124453</v>
       </c>
       <c r="C87">
-        <v>-88.5417540409311</v>
+        <v>-121.0695069396416</v>
       </c>
       <c r="D87">
-        <v>103.4382459590689</v>
+        <v>73.26049306035837</v>
       </c>
       <c r="E87">
-        <v>132.15</v>
+        <v>134.5</v>
       </c>
       <c r="F87">
-        <v>199.75</v>
+        <v>202.1</v>
       </c>
       <c r="G87">
         <v>7.77</v>
@@ -8421,45 +8421,45 @@
         <v>23.5</v>
       </c>
       <c r="M87">
-        <v>29.3233</v>
+        <v>40.58168</v>
       </c>
       <c r="N87">
-        <v>-5.823300000000003</v>
+        <v>-17.08168</v>
       </c>
       <c r="O87">
-        <v>-0.8734950000000005</v>
+        <v>-2.562252</v>
       </c>
       <c r="P87">
-        <v>-4.949805000000003</v>
+        <v>-14.519428</v>
       </c>
       <c r="Q87">
-        <v>2.250194999999996</v>
+        <v>-7.319428</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3651342789701998</v>
+        <v>0.3984155093746092</v>
       </c>
       <c r="T87">
-        <v>5.848719464905805</v>
+        <v>6.458276887647911</v>
       </c>
       <c r="U87">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1202115723673666</v>
+        <v>0.08686185490595758</v>
       </c>
       <c r="W87">
-        <v>0.1291529411764706</v>
+        <v>0.1833581395348837</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.8014104824491104</v>
+        <v>0.5790790327063837</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2134661713124453</v>
+        <v>0.2150161713124453</v>
       </c>
       <c r="C88">
-        <v>-121.0695069396416</v>
+        <v>-124.0905643413239</v>
       </c>
       <c r="D88">
-        <v>73.26049306035837</v>
+        <v>72.58943565867608</v>
       </c>
       <c r="E88">
-        <v>134.5</v>
+        <v>136.85</v>
       </c>
       <c r="F88">
-        <v>202.1</v>
+        <v>204.45</v>
       </c>
       <c r="G88">
         <v>7.77</v>
@@ -8503,37 +8503,37 @@
         <v>23.5</v>
       </c>
       <c r="M88">
-        <v>40.58168</v>
+        <v>41.05356</v>
       </c>
       <c r="N88">
-        <v>-17.08168</v>
+        <v>-17.55356</v>
       </c>
       <c r="O88">
-        <v>-2.562252</v>
+        <v>-2.633033999999999</v>
       </c>
       <c r="P88">
-        <v>-14.519428</v>
+        <v>-14.920526</v>
       </c>
       <c r="Q88">
-        <v>-7.319428</v>
+        <v>-7.720526</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3984155093746092</v>
+        <v>0.4255397793265021</v>
       </c>
       <c r="T88">
-        <v>6.458276887647911</v>
+        <v>6.955067417466981</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.08686185490595758</v>
+        <v>0.08586344278060173</v>
       </c>
       <c r="W88">
-        <v>0.1833581395348837</v>
+        <v>0.1835586206896552</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5790790327063837</v>
+        <v>0.5724229518706783</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2150161713124453</v>
+        <v>0.2165661713124453</v>
       </c>
       <c r="C89">
-        <v>-124.0905643413239</v>
+        <v>-127.099439716969</v>
       </c>
       <c r="D89">
-        <v>72.58943565867608</v>
+        <v>71.93056028303106</v>
       </c>
       <c r="E89">
-        <v>136.85</v>
+        <v>139.2</v>
       </c>
       <c r="F89">
-        <v>204.45</v>
+        <v>206.8</v>
       </c>
       <c r="G89">
         <v>7.77</v>
@@ -8585,37 +8585,37 @@
         <v>23.5</v>
       </c>
       <c r="M89">
-        <v>41.05356</v>
+        <v>41.52544</v>
       </c>
       <c r="N89">
-        <v>-17.55356</v>
+        <v>-18.02544</v>
       </c>
       <c r="O89">
-        <v>-2.633033999999999</v>
+        <v>-2.703816</v>
       </c>
       <c r="P89">
-        <v>-14.920526</v>
+        <v>-15.321624</v>
       </c>
       <c r="Q89">
-        <v>-7.720526</v>
+        <v>-8.121624000000004</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4255397793265021</v>
+        <v>0.4571847609370441</v>
       </c>
       <c r="T89">
-        <v>6.955067417466981</v>
+        <v>7.534656368922565</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.08586344278060173</v>
+        <v>0.08488772183991307</v>
       </c>
       <c r="W89">
-        <v>0.1835586206896552</v>
+        <v>0.1837545454545454</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5724229518706783</v>
+        <v>0.5659181455994204</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2165661713124453</v>
+        <v>0.2181161713124453</v>
       </c>
       <c r="C90">
-        <v>-127.099439716969</v>
+        <v>-130.096461801951</v>
       </c>
       <c r="D90">
-        <v>71.93056028303106</v>
+        <v>71.28353819804902</v>
       </c>
       <c r="E90">
-        <v>139.2</v>
+        <v>141.55</v>
       </c>
       <c r="F90">
-        <v>206.8</v>
+        <v>209.15</v>
       </c>
       <c r="G90">
         <v>7.77</v>
@@ -8667,37 +8667,37 @@
         <v>23.5</v>
       </c>
       <c r="M90">
-        <v>41.52544</v>
+        <v>41.99732</v>
       </c>
       <c r="N90">
-        <v>-18.02544</v>
+        <v>-18.49732</v>
       </c>
       <c r="O90">
-        <v>-2.703816</v>
+        <v>-2.774598</v>
       </c>
       <c r="P90">
-        <v>-15.321624</v>
+        <v>-15.722722</v>
       </c>
       <c r="Q90">
-        <v>-8.121624000000004</v>
+        <v>-8.522722000000002</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4571847609370441</v>
+        <v>0.4945833755676845</v>
       </c>
       <c r="T90">
-        <v>7.534656368922565</v>
+        <v>8.219625129733707</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.08488772183991307</v>
+        <v>0.08393392721249832</v>
       </c>
       <c r="W90">
-        <v>0.1837545454545454</v>
+        <v>0.1839460674157303</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5659181455994204</v>
+        <v>0.5595595147499888</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2181161713124453</v>
+        <v>0.2196661713124453</v>
       </c>
       <c r="C91">
-        <v>-130.096461801951</v>
+        <v>-133.0819476090688</v>
       </c>
       <c r="D91">
-        <v>71.28353819804902</v>
+        <v>70.6480523909312</v>
       </c>
       <c r="E91">
-        <v>141.55</v>
+        <v>143.9</v>
       </c>
       <c r="F91">
-        <v>209.15</v>
+        <v>211.5</v>
       </c>
       <c r="G91">
         <v>7.77</v>
@@ -8749,37 +8749,37 @@
         <v>23.5</v>
       </c>
       <c r="M91">
-        <v>41.99732</v>
+        <v>42.4692</v>
       </c>
       <c r="N91">
-        <v>-18.49732</v>
+        <v>-18.9692</v>
       </c>
       <c r="O91">
-        <v>-2.774598</v>
+        <v>-2.84538</v>
       </c>
       <c r="P91">
-        <v>-15.722722</v>
+        <v>-16.12382</v>
       </c>
       <c r="Q91">
-        <v>-8.522722000000002</v>
+        <v>-8.923820000000003</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4945833755676845</v>
+        <v>0.5394617131244529</v>
       </c>
       <c r="T91">
-        <v>8.219625129733707</v>
+        <v>9.041587642707078</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.08393392721249832</v>
+        <v>0.08300132802124834</v>
       </c>
       <c r="W91">
-        <v>0.1839460674157303</v>
+        <v>0.1841333333333333</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5595595147499888</v>
+        <v>0.5533421868083223</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2196661713124453</v>
+        <v>0.2212161713124453</v>
       </c>
       <c r="C92">
-        <v>-133.0819476090688</v>
+        <v>-136.0562029464567</v>
       </c>
       <c r="D92">
-        <v>70.6480523909312</v>
+        <v>70.0237970535433</v>
       </c>
       <c r="E92">
-        <v>143.9</v>
+        <v>146.25</v>
       </c>
       <c r="F92">
-        <v>211.5</v>
+        <v>213.85</v>
       </c>
       <c r="G92">
         <v>7.77</v>
@@ -8831,37 +8831,37 @@
         <v>23.5</v>
       </c>
       <c r="M92">
-        <v>42.4692</v>
+        <v>42.94108</v>
       </c>
       <c r="N92">
-        <v>-18.9692</v>
+        <v>-19.44108</v>
       </c>
       <c r="O92">
-        <v>-2.84538</v>
+        <v>-2.916162</v>
       </c>
       <c r="P92">
-        <v>-16.12382</v>
+        <v>-16.524918</v>
       </c>
       <c r="Q92">
-        <v>-8.923820000000003</v>
+        <v>-9.324918</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5394617131244529</v>
+        <v>0.5943130145827255</v>
       </c>
       <c r="T92">
-        <v>9.041587642707078</v>
+        <v>10.04620849189675</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.08300132802124834</v>
+        <v>0.08208922551552034</v>
       </c>
       <c r="W92">
-        <v>0.1841333333333333</v>
+        <v>0.1843164835164835</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5533421868083223</v>
+        <v>0.5472615034368022</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2212161713124453</v>
+        <v>0.2227661713124453</v>
       </c>
       <c r="C93">
-        <v>-136.0562029464567</v>
+        <v>-139.0195229082779</v>
       </c>
       <c r="D93">
-        <v>70.0237970535433</v>
+        <v>69.41047709172213</v>
       </c>
       <c r="E93">
-        <v>146.25</v>
+        <v>148.6</v>
       </c>
       <c r="F93">
-        <v>213.85</v>
+        <v>216.2</v>
       </c>
       <c r="G93">
         <v>7.77</v>
@@ -8913,37 +8913,37 @@
         <v>23.5</v>
       </c>
       <c r="M93">
-        <v>42.94108</v>
+        <v>43.41296000000001</v>
       </c>
       <c r="N93">
-        <v>-19.44108</v>
+        <v>-19.91296000000001</v>
       </c>
       <c r="O93">
-        <v>-2.916162</v>
+        <v>-2.986944000000001</v>
       </c>
       <c r="P93">
-        <v>-16.524918</v>
+        <v>-16.926016</v>
       </c>
       <c r="Q93">
-        <v>-9.324918</v>
+        <v>-9.726016000000005</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5943130145827255</v>
+        <v>0.6628771414055663</v>
       </c>
       <c r="T93">
-        <v>10.04620849189675</v>
+        <v>11.30198455338385</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.08208922551552034</v>
+        <v>0.08119695132513424</v>
       </c>
       <c r="W93">
-        <v>0.1843164835164835</v>
+        <v>0.184495652173913</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5472615034368022</v>
+        <v>0.5413130088342282</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2227661713124453</v>
+        <v>0.2243161713124453</v>
       </c>
       <c r="C94">
-        <v>-139.0195229082779</v>
+        <v>-141.9721923398549</v>
       </c>
       <c r="D94">
-        <v>69.41047709172213</v>
+        <v>68.80780766014512</v>
       </c>
       <c r="E94">
-        <v>148.6</v>
+        <v>150.95</v>
       </c>
       <c r="F94">
-        <v>216.2</v>
+        <v>218.55</v>
       </c>
       <c r="G94">
         <v>7.77</v>
@@ -8995,37 +8995,37 @@
         <v>23.5</v>
       </c>
       <c r="M94">
-        <v>43.41296000000001</v>
+        <v>43.88484</v>
       </c>
       <c r="N94">
-        <v>-19.91296000000001</v>
+        <v>-20.38484</v>
       </c>
       <c r="O94">
-        <v>-2.986944000000001</v>
+        <v>-3.057726000000001</v>
       </c>
       <c r="P94">
-        <v>-16.926016</v>
+        <v>-17.327114</v>
       </c>
       <c r="Q94">
-        <v>-9.726016000000005</v>
+        <v>-10.127114</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6628771414055663</v>
+        <v>0.7510310187492188</v>
       </c>
       <c r="T94">
-        <v>11.30198455338385</v>
+        <v>12.91655377529583</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.08119695132513424</v>
+        <v>0.08032386582701452</v>
       </c>
       <c r="W94">
-        <v>0.184495652173913</v>
+        <v>0.1846709677419355</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5413130088342282</v>
+        <v>0.5354924388467635</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2243161713124453</v>
+        <v>0.2258661713124453</v>
       </c>
       <c r="C95">
-        <v>-141.9721923398549</v>
+        <v>-144.9144862787767</v>
       </c>
       <c r="D95">
-        <v>68.80780766014512</v>
+        <v>68.21551372122327</v>
       </c>
       <c r="E95">
-        <v>150.95</v>
+        <v>153.3</v>
       </c>
       <c r="F95">
-        <v>218.55</v>
+        <v>220.9</v>
       </c>
       <c r="G95">
         <v>7.77</v>
@@ -9077,37 +9077,37 @@
         <v>23.5</v>
       </c>
       <c r="M95">
-        <v>43.88484</v>
+        <v>44.35672</v>
       </c>
       <c r="N95">
-        <v>-20.38484</v>
+        <v>-20.85672</v>
       </c>
       <c r="O95">
-        <v>-3.057726000000001</v>
+        <v>-3.128508000000001</v>
       </c>
       <c r="P95">
-        <v>-17.327114</v>
+        <v>-17.728212</v>
       </c>
       <c r="Q95">
-        <v>-10.127114</v>
+        <v>-10.528212</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7510310187492188</v>
+        <v>0.8685695218740888</v>
       </c>
       <c r="T95">
-        <v>12.91655377529583</v>
+        <v>15.06931273784514</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.08032386582701452</v>
+        <v>0.07946935661608882</v>
       </c>
       <c r="W95">
-        <v>0.1846709677419355</v>
+        <v>0.1848425531914894</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5354924388467635</v>
+        <v>0.5297957107739255</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2258661713124453</v>
+        <v>0.2274161713124453</v>
       </c>
       <c r="C96">
-        <v>-144.9144862787767</v>
+        <v>-147.8466703734188</v>
       </c>
       <c r="D96">
-        <v>68.21551372122327</v>
+        <v>67.63332962658119</v>
       </c>
       <c r="E96">
-        <v>153.3</v>
+        <v>155.65</v>
       </c>
       <c r="F96">
-        <v>220.9</v>
+        <v>223.25</v>
       </c>
       <c r="G96">
         <v>7.77</v>
@@ -9159,37 +9159,37 @@
         <v>23.5</v>
       </c>
       <c r="M96">
-        <v>44.35672</v>
+        <v>44.82860000000001</v>
       </c>
       <c r="N96">
-        <v>-20.85672</v>
+        <v>-21.32860000000001</v>
       </c>
       <c r="O96">
-        <v>-3.128508000000001</v>
+        <v>-3.199290000000001</v>
       </c>
       <c r="P96">
-        <v>-17.728212</v>
+        <v>-18.12931000000001</v>
       </c>
       <c r="Q96">
-        <v>-10.528212</v>
+        <v>-10.92931000000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8685695218740888</v>
+        <v>1.033123426248907</v>
       </c>
       <c r="T96">
-        <v>15.06931273784514</v>
+        <v>18.08317528541418</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.07946935661608882</v>
+        <v>0.07863283707276157</v>
       </c>
       <c r="W96">
-        <v>0.1848425531914894</v>
+        <v>0.1850105263157895</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5297957107739255</v>
+        <v>0.5242189138184105</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2274161713124453</v>
+        <v>0.2289661713124453</v>
       </c>
       <c r="C97">
-        <v>-147.8466703734188</v>
+        <v>-150.7690012802126</v>
       </c>
       <c r="D97">
-        <v>67.63332962658119</v>
+        <v>67.06099871978741</v>
       </c>
       <c r="E97">
-        <v>155.65</v>
+        <v>158</v>
       </c>
       <c r="F97">
-        <v>223.25</v>
+        <v>225.6</v>
       </c>
       <c r="G97">
         <v>7.77</v>
@@ -9241,37 +9241,37 @@
         <v>23.5</v>
       </c>
       <c r="M97">
-        <v>44.82860000000001</v>
+        <v>45.30048000000001</v>
       </c>
       <c r="N97">
-        <v>-21.32860000000001</v>
+        <v>-21.80048000000001</v>
       </c>
       <c r="O97">
-        <v>-3.199290000000001</v>
+        <v>-3.270072000000001</v>
       </c>
       <c r="P97">
-        <v>-18.12931000000001</v>
+        <v>-18.530408</v>
       </c>
       <c r="Q97">
-        <v>-10.92931000000001</v>
+        <v>-11.33040800000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.033123426248907</v>
+        <v>1.279954282811134</v>
       </c>
       <c r="T97">
-        <v>18.08317528541418</v>
+        <v>22.60396910676773</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.07863283707276157</v>
+        <v>0.07781374501992029</v>
       </c>
       <c r="W97">
-        <v>0.1850105263157895</v>
+        <v>0.185175</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5242189138184105</v>
+        <v>0.518758300132802</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2289661713124453</v>
+        <v>0.2305161713124453</v>
       </c>
       <c r="C98">
-        <v>-150.7690012802126</v>
+        <v>-153.6817270409141</v>
       </c>
       <c r="D98">
-        <v>67.06099871978741</v>
+        <v>66.49827295908588</v>
       </c>
       <c r="E98">
-        <v>158</v>
+        <v>160.35</v>
       </c>
       <c r="F98">
-        <v>225.6</v>
+        <v>227.95</v>
       </c>
       <c r="G98">
         <v>7.77</v>
@@ -9323,37 +9323,37 @@
         <v>23.5</v>
       </c>
       <c r="M98">
-        <v>45.30048</v>
+        <v>45.77236</v>
       </c>
       <c r="N98">
-        <v>-21.80048</v>
+        <v>-22.27236</v>
       </c>
       <c r="O98">
-        <v>-3.270072</v>
+        <v>-3.340854</v>
       </c>
       <c r="P98">
-        <v>-18.530408</v>
+        <v>-18.931506</v>
       </c>
       <c r="Q98">
-        <v>-11.330408</v>
+        <v>-11.731506</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.279954282811131</v>
+        <v>1.691339043748175</v>
       </c>
       <c r="T98">
-        <v>22.60396910676767</v>
+        <v>30.13862547569023</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.07781374501992032</v>
+        <v>0.07701154146301392</v>
       </c>
       <c r="W98">
-        <v>0.185175</v>
+        <v>0.1853360824742268</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5187583001328021</v>
+        <v>0.5134102764200928</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2305161713124453</v>
+        <v>0.2320661713124453</v>
       </c>
       <c r="C99">
-        <v>-153.6817270409141</v>
+        <v>-156.5850874410358</v>
       </c>
       <c r="D99">
-        <v>66.49827295908588</v>
+        <v>65.94491255896422</v>
       </c>
       <c r="E99">
-        <v>160.35</v>
+        <v>162.7</v>
       </c>
       <c r="F99">
-        <v>227.95</v>
+        <v>230.3</v>
       </c>
       <c r="G99">
         <v>7.77</v>
@@ -9405,37 +9405,37 @@
         <v>23.5</v>
       </c>
       <c r="M99">
-        <v>45.77236</v>
+        <v>46.24424</v>
       </c>
       <c r="N99">
-        <v>-22.27236</v>
+        <v>-22.74424</v>
       </c>
       <c r="O99">
-        <v>-3.340854</v>
+        <v>-3.411636</v>
       </c>
       <c r="P99">
-        <v>-18.931506</v>
+        <v>-19.332604</v>
       </c>
       <c r="Q99">
-        <v>-11.731506</v>
+        <v>-12.132604</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.691339043748175</v>
+        <v>2.514108565622262</v>
       </c>
       <c r="T99">
-        <v>30.13862547569023</v>
+        <v>45.20793821353534</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.07701154146301392</v>
+        <v>0.07622570940726889</v>
       </c>
       <c r="W99">
-        <v>0.1853360824742268</v>
+        <v>0.1854938775510204</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5134102764200928</v>
+        <v>0.5081713960484593</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2320661713124453</v>
+        <v>0.2336161713124453</v>
       </c>
       <c r="C100">
-        <v>-156.5850874410358</v>
+        <v>-159.4793143505299</v>
       </c>
       <c r="D100">
-        <v>65.94491255896422</v>
+        <v>65.40068564947006</v>
       </c>
       <c r="E100">
-        <v>162.7</v>
+        <v>165.05</v>
       </c>
       <c r="F100">
-        <v>230.3</v>
+        <v>232.65</v>
       </c>
       <c r="G100">
         <v>7.77</v>
@@ -9487,37 +9487,37 @@
         <v>23.5</v>
       </c>
       <c r="M100">
-        <v>46.24424</v>
+        <v>46.71612</v>
       </c>
       <c r="N100">
-        <v>-22.74424</v>
+        <v>-23.21612</v>
       </c>
       <c r="O100">
-        <v>-3.411636</v>
+        <v>-3.482418</v>
       </c>
       <c r="P100">
-        <v>-19.332604</v>
+        <v>-19.733702</v>
       </c>
       <c r="Q100">
-        <v>-12.132604</v>
+        <v>-12.53370200000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.514108565622262</v>
+        <v>4.982417131244524</v>
       </c>
       <c r="T100">
-        <v>45.20793821353534</v>
+        <v>90.4158764270707</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.07622570940726889</v>
+        <v>0.07545575274658939</v>
       </c>
       <c r="W100">
-        <v>0.1854938775510204</v>
+        <v>0.1856484848484849</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5081713960484593</v>
+        <v>0.5030383516439293</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2336161713124453</v>
-      </c>
-      <c r="C101">
-        <v>-159.4793143505299</v>
-      </c>
-      <c r="D101">
-        <v>65.40068564947006</v>
-      </c>
-      <c r="E101">
-        <v>165.05</v>
-      </c>
-      <c r="F101">
-        <v>232.65</v>
-      </c>
-      <c r="G101">
-        <v>7.77</v>
-      </c>
-      <c r="H101">
-        <v>167.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>30.7</v>
-      </c>
-      <c r="K101">
-        <v>7.199999999999999</v>
-      </c>
-      <c r="L101">
-        <v>23.5</v>
-      </c>
-      <c r="M101">
-        <v>46.71612</v>
-      </c>
-      <c r="N101">
-        <v>-23.21612</v>
-      </c>
-      <c r="O101">
-        <v>-3.482418</v>
-      </c>
-      <c r="P101">
-        <v>-19.733702</v>
-      </c>
-      <c r="Q101">
-        <v>-12.53370200000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.982417131244524</v>
-      </c>
-      <c r="T101">
-        <v>90.4158764270707</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.07545575274658939</v>
-      </c>
-      <c r="W101">
-        <v>0.1856484848484849</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5030383516439293</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
